--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_9sep26_Wed.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_9sep26_Wed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63747E9-9586-4352-BF68-D33DC05089C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B802963-9EBF-4976-9B67-1FC877D7FAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="N96" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$777, B96, $C$2:$C$777, C96, $D$2:$D$777, D96, $E$2:$E$777, E96) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
+        <v>Duplicate</v>
       </c>
     </row>
     <row r="97" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5573,7 +5573,7 @@
         <v>5</v>
       </c>
       <c r="E97" s="4">
-        <v>4048</v>
+        <v>4047</v>
       </c>
       <c r="F97" s="4">
         <v>2.8716645490000001</v>
@@ -5598,11 +5598,11 @@
       </c>
       <c r="M97" s="18">
         <f>ABS((D97*E97)-L97)</f>
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="N97" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$777, B97, $C$2:$C$777, C97, $D$2:$D$777, D97, $E$2:$E$777, E97) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
+        <v>Duplicate</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">

--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_9sep26_Wed.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_9sep26_Wed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B802963-9EBF-4976-9B67-1FC877D7FAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0640F3C-CB7C-41B2-9444-B350F8FB0E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3233" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3239" uniqueCount="286">
   <si>
     <t>Date</t>
   </si>
@@ -1067,7 +1067,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1271,15 +1271,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1682,7 +1673,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B2, $C$2:$C$777, C2, $D$2:$D$777, D2, $E$2:$E$777, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N33" si="0">IF(COUNTIFS( $B$2:$B$777, B2, $C$2:$C$777, C2, $D$2:$D$777, D2, $E$2:$E$777, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -1721,7 +1712,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B3, $C$2:$C$777, C3, $D$2:$D$777, D3, $E$2:$E$777, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="26"/>
@@ -1760,7 +1751,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B4, $C$2:$C$777, C4, $D$2:$D$777, D4, $E$2:$E$777, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -1801,7 +1792,7 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B5, $C$2:$C$777, C5, $D$2:$D$777, D5, $E$2:$E$777, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -1849,7 +1840,7 @@
         <v>300</v>
       </c>
       <c r="N6" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B6, $C$2:$C$777, C6, $D$2:$D$777, D6, $E$2:$E$777, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="25"/>
@@ -1888,7 +1879,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B7, $C$2:$C$777, C7, $D$2:$D$777, D7, $E$2:$E$777, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="10"/>
@@ -1927,7 +1918,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B8, $C$2:$C$777, C8, $D$2:$D$777, D8, $E$2:$E$777, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="10"/>
@@ -1975,10 +1966,10 @@
         <v>20</v>
       </c>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B9, $C$2:$C$777, C9, $D$2:$D$777, D9, $E$2:$E$777, E9) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O9" s="74"/>
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+      <c r="O9" s="10"/>
       <c r="P9" s="25"/>
     </row>
     <row r="10" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2014,7 +2005,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B10, $C$2:$C$777, C10, $D$2:$D$777, D10, $E$2:$E$777, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="10"/>
@@ -2055,7 +2046,7 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B11, $C$2:$C$777, C11, $D$2:$D$777, D11, $E$2:$E$777, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="10"/>
@@ -2103,7 +2094,7 @@
         <v>300</v>
       </c>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B12, $C$2:$C$777, C12, $D$2:$D$777, D12, $E$2:$E$777, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="10"/>
@@ -2142,7 +2133,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B13, $C$2:$C$777, C13, $D$2:$D$777, D13, $E$2:$E$777, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="19"/>
@@ -2190,7 +2181,7 @@
         <v>460</v>
       </c>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B14, $C$2:$C$777, C14, $D$2:$D$777, D14, $E$2:$E$777, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P14" s="10"/>
@@ -2223,12 +2214,14 @@
       <c r="I15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="41"/>
+      <c r="J15" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B15, $C$2:$C$777, C15, $D$2:$D$777, D15, $E$2:$E$777, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O15" s="10"/>
@@ -2276,7 +2269,7 @@
         <v>222.75</v>
       </c>
       <c r="N16" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B16, $C$2:$C$777, C16, $D$2:$D$777, D16, $E$2:$E$777, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16" s="10"/>
@@ -2315,7 +2308,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B17, $C$2:$C$777, C17, $D$2:$D$777, D17, $E$2:$E$777, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17" s="10"/>
@@ -2356,7 +2349,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B18, $C$2:$C$777, C18, $D$2:$D$777, D18, $E$2:$E$777, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P18" s="10"/>
@@ -2394,7 +2387,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B19, $C$2:$C$777, C19, $D$2:$D$777, D19, $E$2:$E$777, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19" s="10"/>
@@ -2433,7 +2426,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B20, $C$2:$C$777, C20, $D$2:$D$777, D20, $E$2:$E$777, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20" s="10"/>
@@ -2472,7 +2465,7 @@
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B21, $C$2:$C$777, C21, $D$2:$D$777, D21, $E$2:$E$777, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2518,7 +2511,7 @@
         <v>300</v>
       </c>
       <c r="N22" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B22, $C$2:$C$777, C22, $D$2:$D$777, D22, $E$2:$E$777, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22" s="10"/>
@@ -2559,7 +2552,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B23, $C$2:$C$777, C23, $D$2:$D$777, D23, $E$2:$E$777, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23" s="10"/>
@@ -2608,7 +2601,7 @@
         <v>650</v>
       </c>
       <c r="N24" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B24, $C$2:$C$777, C24, $D$2:$D$777, D24, $E$2:$E$777, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P24" s="10"/>
@@ -2655,7 +2648,7 @@
         <v>525</v>
       </c>
       <c r="N25" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B25, $C$2:$C$777, C25, $D$2:$D$777, D25, $E$2:$E$777, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25" s="10"/>
@@ -2694,7 +2687,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B26, $C$2:$C$777, C26, $D$2:$D$777, D26, $E$2:$E$777, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26" s="10"/>
@@ -2728,12 +2721,14 @@
       <c r="I27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J27" s="41"/>
+      <c r="J27" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K27" s="17"/>
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B27, $C$2:$C$777, C27, $D$2:$D$777, D27, $E$2:$E$777, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27" s="10"/>
@@ -2767,12 +2762,14 @@
       <c r="I28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J28" s="41"/>
+      <c r="J28" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B28, $C$2:$C$777, C28, $D$2:$D$777, D28, $E$2:$E$777, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28" s="10"/>
@@ -2813,7 +2810,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B29, $C$2:$C$777, C29, $D$2:$D$777, D29, $E$2:$E$777, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P29" s="10"/>
@@ -2860,7 +2857,7 @@
         <v>300</v>
       </c>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B30, $C$2:$C$777, C30, $D$2:$D$777, D30, $E$2:$E$777, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30" s="10"/>
@@ -2901,7 +2898,7 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B31, $C$2:$C$777, C31, $D$2:$D$777, D31, $E$2:$E$777, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31" s="10"/>
@@ -2934,12 +2931,14 @@
       <c r="I32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="41"/>
+      <c r="J32" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K32" s="17"/>
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B32, $C$2:$C$777, C32, $D$2:$D$777, D32, $E$2:$E$777, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32" s="10"/>
@@ -2987,7 +2986,7 @@
         <v>500</v>
       </c>
       <c r="N33" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B33, $C$2:$C$777, C33, $D$2:$D$777, D33, $E$2:$E$777, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33" s="10"/>
@@ -3028,13 +3027,13 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B34, $C$2:$C$777, C34, $D$2:$D$777, D34, $E$2:$E$777, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N34:N65" si="1">IF(COUNTIFS( $B$2:$B$777, B34, $C$2:$C$777, C34, $D$2:$D$777, D34, $E$2:$E$777, E34) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O34" s="10"/>
       <c r="P34" s="10"/>
     </row>
-    <row r="35" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="6" t="s">
         <v>62</v>
       </c>
@@ -3062,12 +3061,14 @@
       <c r="I35" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J35" s="41"/>
+      <c r="J35" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B35, $C$2:$C$777, C35, $D$2:$D$777, D35, $E$2:$E$777, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3099,12 +3100,14 @@
       <c r="I36" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J36" s="41"/>
+      <c r="J36" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K36" s="17"/>
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B36, $C$2:$C$777, C36, $D$2:$D$777, D36, $E$2:$E$777, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O36" s="34"/>
@@ -3142,7 +3145,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B37, $C$2:$C$777, C37, $D$2:$D$777, D37, $E$2:$E$777, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P37" s="10"/>
@@ -3182,7 +3185,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B38, $C$2:$C$777, C38, $D$2:$D$777, D38, $E$2:$E$777, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O38" s="10"/>
@@ -3221,7 +3224,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B39, $C$2:$C$777, C39, $D$2:$D$777, D39, $E$2:$E$777, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3260,7 +3263,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B40, $C$2:$C$777, C40, $D$2:$D$777, D40, $E$2:$E$777, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3299,7 +3302,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B41, $C$2:$C$777, C41, $D$2:$D$777, D41, $E$2:$E$777, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3336,7 +3339,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B42, $C$2:$C$777, C42, $D$2:$D$777, D42, $E$2:$E$777, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P42" s="10"/>
@@ -3383,7 +3386,7 @@
         <v>300</v>
       </c>
       <c r="N43" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B43, $C$2:$C$777, C43, $D$2:$D$777, D43, $E$2:$E$777, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3420,7 +3423,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B44, $C$2:$C$777, C44, $D$2:$D$777, D44, $E$2:$E$777, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3457,7 +3460,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B45, $C$2:$C$777, C45, $D$2:$D$777, D45, $E$2:$E$777, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3496,7 +3499,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B46, $C$2:$C$777, C46, $D$2:$D$777, D46, $E$2:$E$777, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3543,7 +3546,7 @@
         <v>540</v>
       </c>
       <c r="N47" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B47, $C$2:$C$777, C47, $D$2:$D$777, D47, $E$2:$E$777, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -3591,7 +3594,7 @@
         <v>450</v>
       </c>
       <c r="N48" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B48, $C$2:$C$777, C48, $D$2:$D$777, D48, $E$2:$E$777, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3637,7 +3640,7 @@
         <v>516</v>
       </c>
       <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B49, $C$2:$C$777, C49, $D$2:$D$777, D49, $E$2:$E$777, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3683,7 +3686,7 @@
         <v>300</v>
       </c>
       <c r="N50" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B50, $C$2:$C$777, C50, $D$2:$D$777, D50, $E$2:$E$777, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P50" s="25"/>
@@ -3723,7 +3726,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B51, $C$2:$C$777, C51, $D$2:$D$777, D51, $E$2:$E$777, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O51"/>
@@ -3762,7 +3765,7 @@
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B52, $C$2:$C$777, C52, $D$2:$D$777, D52, $E$2:$E$777, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O52"/>
@@ -3810,7 +3813,7 @@
         <v>300</v>
       </c>
       <c r="N53" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B53, $C$2:$C$777, C53, $D$2:$D$777, D53, $E$2:$E$777, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O53"/>
@@ -3852,7 +3855,7 @@
         <v>3156</v>
       </c>
       <c r="N54" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B54, $C$2:$C$777, C54, $D$2:$D$777, D54, $E$2:$E$777, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P54" s="19"/>
@@ -3892,7 +3895,7 @@
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B55, $C$2:$C$777, C55, $D$2:$D$777, D55, $E$2:$E$777, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -3933,7 +3936,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B56, $C$2:$C$777, C56, $D$2:$D$777, D56, $E$2:$E$777, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O56"/>
@@ -3972,7 +3975,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B57, $C$2:$C$777, C57, $D$2:$D$777, D57, $E$2:$E$777, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
@@ -4011,7 +4014,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B58, $C$2:$C$777, C58, $D$2:$D$777, D58, $E$2:$E$777, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P58"/>
@@ -4049,7 +4052,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B59, $C$2:$C$777, C59, $D$2:$D$777, D59, $E$2:$E$777, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P59" s="10"/>
@@ -4089,7 +4092,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B60, $C$2:$C$777, C60, $D$2:$D$777, D60, $E$2:$E$777, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O60"/>
@@ -4128,7 +4131,7 @@
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B61, $C$2:$C$777, C61, $D$2:$D$777, D61, $E$2:$E$777, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O61"/>
@@ -4169,7 +4172,7 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B62, $C$2:$C$777, C62, $D$2:$D$777, D62, $E$2:$E$777, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P62"/>
@@ -4209,7 +4212,7 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B63, $C$2:$C$777, C63, $D$2:$D$777, D63, $E$2:$E$777, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O63"/>
@@ -4248,7 +4251,7 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B64, $C$2:$C$777, C64, $D$2:$D$777, D64, $E$2:$E$777, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
@@ -4289,7 +4292,7 @@
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B65, $C$2:$C$777, C65, $D$2:$D$777, D65, $E$2:$E$777, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O65"/>
@@ -4332,7 +4335,7 @@
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B66, $C$2:$C$777, C66, $D$2:$D$777, D66, $E$2:$E$777, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N93" si="2">IF(COUNTIFS( $B$2:$B$777, B66, $C$2:$C$777, C66, $D$2:$D$777, D66, $E$2:$E$777, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66"/>
@@ -4371,7 +4374,7 @@
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B67, $C$2:$C$777, C67, $D$2:$D$777, D67, $E$2:$E$777, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O67"/>
@@ -4410,7 +4413,7 @@
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B68, $C$2:$C$777, C68, $D$2:$D$777, D68, $E$2:$E$777, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O68"/>
@@ -4449,7 +4452,7 @@
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B69, $C$2:$C$777, C69, $D$2:$D$777, D69, $E$2:$E$777, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O69"/>
@@ -4488,7 +4491,7 @@
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B70, $C$2:$C$777, C70, $D$2:$D$777, D70, $E$2:$E$777, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O70"/>
@@ -4529,13 +4532,13 @@
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B71, $C$2:$C$777, C71, $D$2:$D$777, D71, $E$2:$E$777, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O71"/>
       <c r="P71"/>
     </row>
-    <row r="72" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="6" t="s">
         <v>62</v>
       </c>
@@ -4568,7 +4571,7 @@
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B72, $C$2:$C$777, C72, $D$2:$D$777, D72, $E$2:$E$777, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O72"/>
@@ -4616,7 +4619,7 @@
         <v>300</v>
       </c>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B73, $C$2:$C$777, C73, $D$2:$D$777, D73, $E$2:$E$777, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O73"/>
@@ -4655,13 +4658,13 @@
       <c r="L74" s="17"/>
       <c r="M74" s="17"/>
       <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B74, $C$2:$C$777, C74, $D$2:$D$777, D74, $E$2:$E$777, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O74"/>
       <c r="P74" s="34"/>
     </row>
-    <row r="75" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="6" t="s">
         <v>62</v>
       </c>
@@ -4696,7 +4699,7 @@
       <c r="L75" s="17"/>
       <c r="M75" s="17"/>
       <c r="N75" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B75, $C$2:$C$777, C75, $D$2:$D$777, D75, $E$2:$E$777, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O75"/>
@@ -4735,7 +4738,7 @@
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B76, $C$2:$C$777, C76, $D$2:$D$777, D76, $E$2:$E$777, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O76"/>
@@ -4774,7 +4777,7 @@
       <c r="L77" s="17"/>
       <c r="M77" s="17"/>
       <c r="N77" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B77, $C$2:$C$777, C77, $D$2:$D$777, D77, $E$2:$E$777, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O77"/>
@@ -4813,7 +4816,7 @@
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B78, $C$2:$C$777, C78, $D$2:$D$777, D78, $E$2:$E$777, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O78"/>
@@ -4854,7 +4857,7 @@
       <c r="L79" s="17"/>
       <c r="M79" s="17"/>
       <c r="N79" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B79, $C$2:$C$777, C79, $D$2:$D$777, D79, $E$2:$E$777, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O79"/>
@@ -4902,7 +4905,7 @@
         <v>442</v>
       </c>
       <c r="N80" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B80, $C$2:$C$777, C80, $D$2:$D$777, D80, $E$2:$E$777, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O80"/>
@@ -4941,7 +4944,7 @@
       <c r="L81" s="17"/>
       <c r="M81" s="17"/>
       <c r="N81" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B81, $C$2:$C$777, C81, $D$2:$D$777, D81, $E$2:$E$777, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O81"/>
@@ -4980,13 +4983,13 @@
       <c r="L82" s="17"/>
       <c r="M82" s="17"/>
       <c r="N82" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B82, $C$2:$C$777, C82, $D$2:$D$777, D82, $E$2:$E$777, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O82"/>
       <c r="P82"/>
     </row>
-    <row r="83" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="6" t="s">
         <v>62</v>
       </c>
@@ -5019,7 +5022,7 @@
       <c r="L83" s="17"/>
       <c r="M83" s="17"/>
       <c r="N83" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B83, $C$2:$C$777, C83, $D$2:$D$777, D83, $E$2:$E$777, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O83"/>
@@ -5058,7 +5061,7 @@
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B84, $C$2:$C$777, C84, $D$2:$D$777, D84, $E$2:$E$777, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O84"/>
@@ -5097,7 +5100,7 @@
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B85, $C$2:$C$777, C85, $D$2:$D$777, D85, $E$2:$E$777, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O85"/>
@@ -5136,13 +5139,13 @@
       <c r="L86" s="17"/>
       <c r="M86" s="17"/>
       <c r="N86" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B86, $C$2:$C$777, C86, $D$2:$D$777, D86, $E$2:$E$777, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O86"/>
       <c r="P86"/>
     </row>
-    <row r="87" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="6" t="s">
         <v>62</v>
       </c>
@@ -5175,7 +5178,7 @@
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
       <c r="N87" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B87, $C$2:$C$777, C87, $D$2:$D$777, D87, $E$2:$E$777, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O87"/>
@@ -5214,13 +5217,13 @@
       <c r="L88" s="17"/>
       <c r="M88" s="17"/>
       <c r="N88" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B88, $C$2:$C$777, C88, $D$2:$D$777, D88, $E$2:$E$777, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O88"/>
       <c r="P88"/>
     </row>
-    <row r="89" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="6" t="s">
         <v>62</v>
       </c>
@@ -5255,7 +5258,7 @@
       <c r="L89" s="17"/>
       <c r="M89" s="17"/>
       <c r="N89" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B89, $C$2:$C$777, C89, $D$2:$D$777, D89, $E$2:$E$777, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O89"/>
@@ -5294,7 +5297,7 @@
       <c r="L90" s="17"/>
       <c r="M90" s="17"/>
       <c r="N90" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B90, $C$2:$C$777, C90, $D$2:$D$777, D90, $E$2:$E$777, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O90"/>
@@ -5333,7 +5336,7 @@
       <c r="L91" s="17"/>
       <c r="M91" s="17"/>
       <c r="N91" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B91, $C$2:$C$777, C91, $D$2:$D$777, D91, $E$2:$E$777, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O91"/>
@@ -5372,7 +5375,7 @@
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B92, $C$2:$C$777, C92, $D$2:$D$777, D92, $E$2:$E$777, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O92"/>
@@ -5411,13 +5414,13 @@
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
       <c r="N93" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B93, $C$2:$C$777, C93, $D$2:$D$777, D93, $E$2:$E$777, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O93"/>
       <c r="P93"/>
     </row>
-    <row r="94" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="3">
         <v>46265.392361111109</v>
       </c>
@@ -5455,11 +5458,11 @@
         <v>55382.5</v>
       </c>
       <c r="M94" s="18">
-        <f>ABS((D94*E94)-L94)</f>
+        <f t="shared" ref="M94:M109" si="3">ABS((D94*E94)-L94)</f>
         <v>1567.5</v>
       </c>
       <c r="N94" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B94, $C$2:$C$777, C94, $D$2:$D$777, D94, $E$2:$E$777, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N94:N129" si="4">IF(COUNTIFS( $B$2:$B$777, B94, $C$2:$C$777, C94, $D$2:$D$777, D94, $E$2:$E$777, E94) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O94" s="46" t="s">
@@ -5467,7 +5470,7 @@
       </c>
       <c r="P94"/>
     </row>
-    <row r="95" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="3">
         <v>46274.375659722224</v>
       </c>
@@ -5505,15 +5508,15 @@
         <v>11660</v>
       </c>
       <c r="M95" s="18">
-        <f>ABS((D95*E95)-L95)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B95, $C$2:$C$777, C95, $D$2:$D$777, D95, $E$2:$E$777, E95) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="11">
         <v>46273.375</v>
       </c>
@@ -5551,15 +5554,15 @@
         <v>19730.5</v>
       </c>
       <c r="M96" s="33">
-        <f>ABS((D96*E96)-L96)</f>
+        <f t="shared" si="3"/>
         <v>504.5</v>
       </c>
       <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B96, $C$2:$C$777, C96, $D$2:$D$777, D96, $E$2:$E$777, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="97" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="3">
         <v>46274.375</v>
       </c>
@@ -5597,15 +5600,15 @@
         <v>19690</v>
       </c>
       <c r="M97" s="18">
-        <f>ABS((D97*E97)-L97)</f>
+        <f t="shared" si="3"/>
         <v>545</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B97, $C$2:$C$777, C97, $D$2:$D$777, D97, $E$2:$E$777, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="3">
         <v>46267.375</v>
       </c>
@@ -5643,18 +5646,18 @@
         <v>8220</v>
       </c>
       <c r="M98" s="18">
-        <f>ABS((D98*E98)-L98)</f>
+        <f t="shared" si="3"/>
         <v>360</v>
       </c>
       <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B98, $C$2:$C$777, C98, $D$2:$D$777, D98, $E$2:$E$777, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O98" s="46" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="11">
         <v>46273.375</v>
       </c>
@@ -5692,18 +5695,18 @@
         <v>9170</v>
       </c>
       <c r="M99" s="33">
-        <f>ABS((D99*E99)-L99)</f>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B99, $C$2:$C$777, C99, $D$2:$D$777, D99, $E$2:$E$777, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O99" s="46" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="3">
         <v>46274.375648148147</v>
       </c>
@@ -5741,15 +5744,15 @@
         <v>16807</v>
       </c>
       <c r="M100" s="18">
-        <f>ABS((D100*E100)-L100)</f>
+        <f t="shared" si="3"/>
         <v>651</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B100, $C$2:$C$777, C100, $D$2:$D$777, D100, $E$2:$E$777, E100) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3">
         <v>46269.614583333336</v>
       </c>
@@ -5787,18 +5790,18 @@
         <v>8480</v>
       </c>
       <c r="M101" s="27">
-        <f>ABS((D101*E101)-L101)</f>
+        <f t="shared" si="3"/>
         <v>280</v>
       </c>
       <c r="N101" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B101, $C$2:$C$777, C101, $D$2:$D$777, D101, $E$2:$E$777, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O101" s="46" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="102" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="36">
         <v>46267.375</v>
       </c>
@@ -5826,7 +5829,7 @@
       <c r="I102" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J102" s="72" t="s">
+      <c r="J102" s="33" t="s">
         <v>118</v>
       </c>
       <c r="K102" s="33" t="s">
@@ -5836,11 +5839,11 @@
         <v>5755</v>
       </c>
       <c r="M102" s="33">
-        <f>ABS((D102*E102)-L102)</f>
+        <f t="shared" si="3"/>
         <v>275</v>
       </c>
       <c r="N102" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B102, $C$2:$C$777, C102, $D$2:$D$777, D102, $E$2:$E$777, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
       <c r="O102" s="46" t="s">
@@ -5848,7 +5851,7 @@
       </c>
       <c r="P102" s="10"/>
     </row>
-    <row r="103" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="36">
         <v>46267.375</v>
       </c>
@@ -5876,7 +5879,7 @@
       <c r="I103" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J103" s="72" t="s">
+      <c r="J103" s="33" t="s">
         <v>118</v>
       </c>
       <c r="K103" s="33" t="s">
@@ -5886,11 +5889,11 @@
         <v>5805</v>
       </c>
       <c r="M103" s="33">
-        <f>ABS((D103*E103)-L103)</f>
+        <f t="shared" si="3"/>
         <v>225</v>
       </c>
       <c r="N103" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B103, $C$2:$C$777, C103, $D$2:$D$777, D103, $E$2:$E$777, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
       <c r="O103" s="46" t="s">
@@ -5898,7 +5901,7 @@
       </c>
       <c r="P103" s="10"/>
     </row>
-    <row r="104" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="11">
         <v>46243.375</v>
       </c>
@@ -5936,16 +5939,16 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M104" s="33">
-        <f>ABS((D104*E104)-L104)</f>
+        <f t="shared" si="3"/>
         <v>710.99999999999636</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B104, $C$2:$C$777, C104, $D$2:$D$777, D104, $E$2:$E$777, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O104" s="10"/>
     </row>
-    <row r="105" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3">
         <v>46266.375</v>
       </c>
@@ -5973,7 +5976,7 @@
       <c r="I105" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J105" s="71" t="s">
+      <c r="J105" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K105" s="18" t="s">
@@ -5983,11 +5986,11 @@
         <v>25300</v>
       </c>
       <c r="M105" s="18">
-        <f>ABS((D105*E105)-L105)</f>
+        <f t="shared" si="3"/>
         <v>650</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B105, $C$2:$C$777, C105, $D$2:$D$777, D105, $E$2:$E$777, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O105" s="46" t="s">
@@ -5995,7 +5998,7 @@
       </c>
       <c r="P105" s="10"/>
     </row>
-    <row r="106" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3">
         <v>46267.513888888891</v>
       </c>
@@ -6023,7 +6026,7 @@
       <c r="I106" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J106" s="71" t="s">
+      <c r="J106" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K106" s="18" t="s">
@@ -6033,11 +6036,11 @@
         <v>12480</v>
       </c>
       <c r="M106" s="18">
-        <f>ABS((D106*E106)-L106)</f>
+        <f t="shared" si="3"/>
         <v>495</v>
       </c>
       <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B106, $C$2:$C$777, C106, $D$2:$D$777, D106, $E$2:$E$777, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O106" s="46" t="s">
@@ -6045,7 +6048,7 @@
       </c>
       <c r="P106" s="10"/>
     </row>
-    <row r="107" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -6083,18 +6086,18 @@
         <v>20010</v>
       </c>
       <c r="M107" s="18">
-        <f>ABS((D107*E107)-L107)</f>
+        <f t="shared" si="3"/>
         <v>450</v>
       </c>
       <c r="N107" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B107, $C$2:$C$777, C107, $D$2:$D$777, D107, $E$2:$E$777, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="46" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="108" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3">
         <v>46261.375</v>
       </c>
@@ -6132,16 +6135,16 @@
         <v>14440</v>
       </c>
       <c r="M108" s="18">
-        <f>ABS((D108*E108)-L108)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B108, $C$2:$C$777, C108, $D$2:$D$777, D108, $E$2:$E$777, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="P108" s="10"/>
     </row>
-    <row r="109" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="11">
         <v>46273.375</v>
       </c>
@@ -6169,7 +6172,7 @@
       <c r="I109" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J109" s="71" t="s">
+      <c r="J109" s="18" t="s">
         <v>156</v>
       </c>
       <c r="K109" s="18" t="s">
@@ -6179,17 +6182,17 @@
         <v>9170</v>
       </c>
       <c r="M109" s="33">
-        <f>ABS((D109*E109)-L109)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B109, $C$2:$C$777, C109, $D$2:$D$777, D109, $E$2:$E$777, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="10"/>
       <c r="P109" s="10"/>
     </row>
-    <row r="110" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6219,7 +6222,7 @@
       </c>
       <c r="J110" s="40"/>
       <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B110, $C$2:$C$777, C110, $D$2:$D$777, D110, $E$2:$E$777, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O110" s="46" t="s">
@@ -6227,7 +6230,7 @@
       </c>
       <c r="P110"/>
     </row>
-    <row r="111" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="36">
         <v>46262.375</v>
       </c>
@@ -6265,11 +6268,11 @@
         <v>3560</v>
       </c>
       <c r="M111" s="33">
-        <f>ABS((D111*E111)-L111)</f>
+        <f t="shared" ref="M111:M118" si="5">ABS((D111*E111)-L111)</f>
         <v>175</v>
       </c>
       <c r="N111" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B111, $C$2:$C$777, C111, $D$2:$D$777, D111, $E$2:$E$777, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
       <c r="O111" s="46" t="s">
@@ -6277,7 +6280,7 @@
       </c>
       <c r="P111"/>
     </row>
-    <row r="112" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="36">
         <v>46265.375694444447</v>
       </c>
@@ -6315,11 +6318,11 @@
         <v>3510</v>
       </c>
       <c r="M112" s="33">
-        <f>ABS((D112*E112)-L112)</f>
+        <f t="shared" si="5"/>
         <v>225</v>
       </c>
       <c r="N112" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B112, $C$2:$C$777, C112, $D$2:$D$777, D112, $E$2:$E$777, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
       <c r="O112" s="46" t="s">
@@ -6327,7 +6330,7 @@
       </c>
       <c r="P112" s="10"/>
     </row>
-    <row r="113" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -6365,11 +6368,11 @@
         <v>25780</v>
       </c>
       <c r="M113" s="18">
-        <f>ABS((D113*E113)-L113)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N113" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B113, $C$2:$C$777, C113, $D$2:$D$777, D113, $E$2:$E$777, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O113" s="46" t="s">
@@ -6377,7 +6380,7 @@
       </c>
       <c r="P113"/>
     </row>
-    <row r="114" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3">
         <v>46260.375694444447</v>
       </c>
@@ -6415,16 +6418,16 @@
         <v>20260</v>
       </c>
       <c r="M114" s="18">
-        <f>ABS((D114*E114)-L114)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N114" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B114, $C$2:$C$777, C114, $D$2:$D$777, D114, $E$2:$E$777, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O114"/>
     </row>
-    <row r="115" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -6462,15 +6465,15 @@
         <v>15075</v>
       </c>
       <c r="M115" s="18">
-        <f>ABS((D115*E115)-L115)</f>
+        <f t="shared" si="5"/>
         <v>645</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B115, $C$2:$C$777, C115, $D$2:$D$777, D115, $E$2:$E$777, E115) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" s="19" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" s="19" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3">
         <v>46262.375</v>
       </c>
@@ -6508,17 +6511,17 @@
         <v>8420</v>
       </c>
       <c r="M116" s="18">
-        <f>ABS((D116*E116)-L116)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B116, $C$2:$C$777, C116, $D$2:$D$777, D116, $E$2:$E$777, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O116" s="10"/>
       <c r="P116" s="10"/>
     </row>
-    <row r="117" spans="1:16" s="26" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:16" s="26" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3">
         <v>46265.390277777777</v>
       </c>
@@ -6556,17 +6559,17 @@
         <v>25530</v>
       </c>
       <c r="M117" s="18">
-        <f>ABS((D117*E117)-L117)</f>
+        <f t="shared" si="5"/>
         <v>650</v>
       </c>
       <c r="N117" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B117, $C$2:$C$777, C117, $D$2:$D$777, D117, $E$2:$E$777, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O117"/>
       <c r="P117"/>
     </row>
-    <row r="118" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="3">
         <v>46274.375659722224</v>
       </c>
@@ -6604,15 +6607,15 @@
         <v>20070</v>
       </c>
       <c r="M118" s="18">
-        <f>ABS((D118*E118)-L118)</f>
+        <f t="shared" si="5"/>
         <v>810</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B118, $C$2:$C$777, C118, $D$2:$D$777, D118, $E$2:$E$777, E118) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6642,11 +6645,11 @@
       </c>
       <c r="J119" s="40"/>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B119, $C$2:$C$777, C119, $D$2:$D$777, D119, $E$2:$E$777, E119) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" s="25" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" s="25" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="8" t="s">
         <v>62</v>
       </c>
@@ -6679,13 +6682,13 @@
       <c r="L120" s="18"/>
       <c r="M120" s="18"/>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B120, $C$2:$C$777, C120, $D$2:$D$777, D120, $E$2:$E$777, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O120" s="10"/>
       <c r="P120" s="10"/>
     </row>
-    <row r="121" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -6727,11 +6730,11 @@
         <v>290</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B121, $C$2:$C$777, C121, $D$2:$D$777, D121, $E$2:$E$777, E121) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3">
         <v>46267.375</v>
       </c>
@@ -6773,12 +6776,12 @@
         <v>300</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B122, $C$2:$C$777, C122, $D$2:$D$777, D122, $E$2:$E$777, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="P122" s="19"/>
     </row>
-    <row r="123" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="11">
         <v>46243.375</v>
       </c>
@@ -6820,12 +6823,12 @@
         <v>300</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B123, $C$2:$C$777, C123, $D$2:$D$777, D123, $E$2:$E$777, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="P123" s="26"/>
     </row>
-    <row r="124" spans="1:16" s="25" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -6867,13 +6870,13 @@
         <v>340</v>
       </c>
       <c r="N124" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B124, $C$2:$C$777, C124, $D$2:$D$777, D124, $E$2:$E$777, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O124" s="10"/>
       <c r="P124" s="10"/>
     </row>
-    <row r="125" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="3">
         <v>46266.375</v>
       </c>
@@ -6915,12 +6918,12 @@
         <v>300</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B125, $C$2:$C$777, C125, $D$2:$D$777, D125, $E$2:$E$777, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="P125" s="35"/>
     </row>
-    <row r="126" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6952,11 +6955,11 @@
         <v>117</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B126, $C$2:$C$777, C126, $D$2:$D$777, D126, $E$2:$E$777, E126) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="36">
         <v>46269.542361111111</v>
       </c>
@@ -6998,7 +7001,7 @@
         <v>300.00000000000182</v>
       </c>
       <c r="N127" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B127, $C$2:$C$777, C127, $D$2:$D$777, D127, $E$2:$E$777, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O127" s="46" t="s">
@@ -7006,7 +7009,7 @@
       </c>
       <c r="P127" s="35"/>
     </row>
-    <row r="128" spans="1:16" s="26" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:16" s="26" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="36">
         <v>46272.530555555553</v>
       </c>
@@ -7048,7 +7051,7 @@
         <v>274</v>
       </c>
       <c r="N128" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B128, $C$2:$C$777, C128, $D$2:$D$777, D128, $E$2:$E$777, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="46" t="s">
@@ -7056,7 +7059,7 @@
       </c>
       <c r="P128" s="35"/>
     </row>
-    <row r="129" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="3">
         <v>46262.463194444441</v>
       </c>
@@ -7098,11 +7101,11 @@
         <v>300</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B129, $C$2:$C$777, C129, $D$2:$D$777, D129, $E$2:$E$777, E129) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3">
         <v>46267.425694444442</v>
       </c>
@@ -7144,14 +7147,14 @@
         <v>270</v>
       </c>
       <c r="N130" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B130, $C$2:$C$777, C130, $D$2:$D$777, D130, $E$2:$E$777, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="6">IF(COUNTIFS( $B$2:$B$777, B130, $C$2:$C$777, C130, $D$2:$D$777, D130, $E$2:$E$777, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="47" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="131" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="11">
         <v>46252.645833333336</v>
       </c>
@@ -7184,13 +7187,13 @@
       <c r="L131" s="18"/>
       <c r="M131" s="18"/>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B131, $C$2:$C$777, C131, $D$2:$D$777, D131, $E$2:$E$777, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O131" s="25"/>
       <c r="P131" s="10"/>
     </row>
-    <row r="132" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -7225,7 +7228,7 @@
       <c r="L132" s="18"/>
       <c r="M132" s="18"/>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B132, $C$2:$C$777, C132, $D$2:$D$777, D132, $E$2:$E$777, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O132" s="46" t="s">
@@ -7233,7 +7236,7 @@
       </c>
       <c r="P132"/>
     </row>
-    <row r="133" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="11">
         <v>46252.6875</v>
       </c>
@@ -7265,14 +7268,14 @@
         <v>118</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B133, $C$2:$C$777, C133, $D$2:$D$777, D133, $E$2:$E$777, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O133" s="46" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="134" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="63">
         <v>46265.375694444447</v>
       </c>
@@ -7310,11 +7313,11 @@
         <v>5905</v>
       </c>
       <c r="M134" s="62">
-        <f>ABS((D134*E134)-L134)</f>
+        <f t="shared" ref="M134:M141" si="7">ABS((D134*E134)-L134)</f>
         <v>275</v>
       </c>
       <c r="N134" s="64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B134, $C$2:$C$777, C134, $D$2:$D$777, D134, $E$2:$E$777, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="25"/>
@@ -7322,7 +7325,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3">
         <v>46274.375</v>
       </c>
@@ -7360,15 +7363,15 @@
         <v>4852</v>
       </c>
       <c r="M135" s="18">
-        <f>ABS((D135*E135)-L135)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B135, $C$2:$C$777, C135, $D$2:$D$777, D135, $E$2:$E$777, E135) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -7406,15 +7409,15 @@
         <v>17040</v>
       </c>
       <c r="M136" s="18">
-        <f>ABS((D136*E136)-L136)</f>
+        <f t="shared" si="7"/>
         <v>880</v>
       </c>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B136, $C$2:$C$777, C136, $D$2:$D$777, D136, $E$2:$E$777, E136) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3">
         <v>46262.375</v>
       </c>
@@ -7452,15 +7455,15 @@
         <v>26300</v>
       </c>
       <c r="M137" s="18">
-        <f>ABS((D137*E137)-L137)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B137, $C$2:$C$777, C137, $D$2:$D$777, D137, $E$2:$E$777, E137) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="3">
         <v>46266.375</v>
       </c>
@@ -7498,15 +7501,15 @@
         <v>12600</v>
       </c>
       <c r="M138" s="18">
-        <f>ABS((D138*E138)-L138)</f>
+        <f t="shared" si="7"/>
         <v>360</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B138, $C$2:$C$777, C138, $D$2:$D$777, D138, $E$2:$E$777, E138) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="3">
         <v>46267.375</v>
       </c>
@@ -7544,16 +7547,16 @@
         <v>3005</v>
       </c>
       <c r="M139" s="18">
-        <f>ABS((D139*E139)-L139)</f>
+        <f t="shared" si="7"/>
         <v>240</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B139, $C$2:$C$777, C139, $D$2:$D$777, D139, $E$2:$E$777, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P139" s="26"/>
     </row>
-    <row r="140" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="3">
         <v>46267.375</v>
       </c>
@@ -7591,15 +7594,15 @@
         <v>4080</v>
       </c>
       <c r="M140" s="18">
-        <f>ABS((D140*E140)-L140)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B140, $C$2:$C$777, C140, $D$2:$D$777, D140, $E$2:$E$777, E140) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="3">
         <v>46262.375</v>
       </c>
@@ -7637,16 +7640,16 @@
         <v>10410</v>
       </c>
       <c r="M141" s="18">
-        <f>ABS((D141*E141)-L141)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B141, $C$2:$C$777, C141, $D$2:$D$777, D141, $E$2:$E$777, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O141" s="35"/>
     </row>
-    <row r="142" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -7683,11 +7686,11 @@
       <c r="L142" s="17"/>
       <c r="M142" s="17"/>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B142, $C$2:$C$777, C142, $D$2:$D$777, D142, $E$2:$E$777, E142) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" s="25" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="8" t="s">
         <v>62</v>
       </c>
@@ -7720,13 +7723,13 @@
       <c r="L143" s="18"/>
       <c r="M143" s="18"/>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B143, $C$2:$C$777, C143, $D$2:$D$777, D143, $E$2:$E$777, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="10"/>
       <c r="P143" s="10"/>
     </row>
-    <row r="144" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="3">
         <v>46268.375</v>
       </c>
@@ -7764,15 +7767,15 @@
         <v>32200</v>
       </c>
       <c r="M144" s="18">
-        <f>ABS((D144*E144)-L144)</f>
+        <f t="shared" ref="M144:M151" si="8">ABS((D144*E144)-L144)</f>
         <v>1200</v>
       </c>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B144, $C$2:$C$777, C144, $D$2:$D$777, D144, $E$2:$E$777, E144) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -7800,7 +7803,7 @@
       <c r="I145" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J145" s="71" t="s">
+      <c r="J145" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K145" s="18" t="s">
@@ -7810,18 +7813,18 @@
         <v>5940</v>
       </c>
       <c r="M145" s="18">
-        <f>ABS((D145*E145)-L145)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B145, $C$2:$C$777, C145, $D$2:$D$777, D145, $E$2:$E$777, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O145" s="46" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="146" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="3">
         <v>46265.460416666669</v>
       </c>
@@ -7859,11 +7862,11 @@
         <v>8810</v>
       </c>
       <c r="M146" s="18">
-        <f>ABS((D146*E146)-L146)</f>
+        <f t="shared" si="8"/>
         <v>650</v>
       </c>
       <c r="N146" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B146, $C$2:$C$777, C146, $D$2:$D$777, D146, $E$2:$E$777, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="46" t="s">
@@ -7871,7 +7874,7 @@
       </c>
       <c r="P146" s="35"/>
     </row>
-    <row r="147" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="56">
         <v>46273.385416666664</v>
       </c>
@@ -7909,11 +7912,11 @@
         <v>16580</v>
       </c>
       <c r="M147" s="62">
-        <f>ABS((D147*E147)-L147)</f>
+        <f t="shared" si="8"/>
         <v>750</v>
       </c>
       <c r="N147" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B147, $C$2:$C$777, C147, $D$2:$D$777, D147, $E$2:$E$777, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O147" s="25"/>
@@ -7921,7 +7924,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="148" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="11">
         <v>46243.375</v>
       </c>
@@ -7959,18 +7962,18 @@
         <v>8570</v>
       </c>
       <c r="M148" s="33">
-        <f>ABS((D148*E148)-L148)</f>
+        <f t="shared" si="8"/>
         <v>650</v>
       </c>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B148, $C$2:$C$777, C148, $D$2:$D$777, D148, $E$2:$E$777, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O148" s="46" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -8008,15 +8011,15 @@
         <v>9470</v>
       </c>
       <c r="M149" s="18">
-        <f>ABS((D149*E149)-L149)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B149, $C$2:$C$777, C149, $D$2:$D$777, D149, $E$2:$E$777, E149) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="36">
         <v>46260.556944444441</v>
       </c>
@@ -8054,15 +8057,15 @@
         <v>6105</v>
       </c>
       <c r="M150" s="33">
-        <f>ABS((D150*E150)-L150)</f>
+        <f t="shared" si="8"/>
         <v>150</v>
       </c>
       <c r="N150" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B150, $C$2:$C$777, C150, $D$2:$D$777, D150, $E$2:$E$777, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="151" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="36">
         <v>46261.375</v>
       </c>
@@ -8100,15 +8103,15 @@
         <v>6005</v>
       </c>
       <c r="M151" s="33">
-        <f>ABS((D151*E151)-L151)</f>
+        <f t="shared" si="8"/>
         <v>250</v>
       </c>
       <c r="N151" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B151, $C$2:$C$777, C151, $D$2:$D$777, D151, $E$2:$E$777, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="152" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -8138,12 +8141,12 @@
       </c>
       <c r="J152" s="40"/>
       <c r="N152" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B152, $C$2:$C$777, C152, $D$2:$D$777, D152, $E$2:$E$777, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O152" s="35"/>
     </row>
-    <row r="153" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -8185,14 +8188,14 @@
         <v>500</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B153, $C$2:$C$777, C153, $D$2:$D$777, D153, $E$2:$E$777, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O153" s="47" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="154" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="3">
         <v>46266.375</v>
       </c>
@@ -8234,7 +8237,7 @@
         <v>300</v>
       </c>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B154, $C$2:$C$777, C154, $D$2:$D$777, D154, $E$2:$E$777, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O154" s="46" t="s">
@@ -8284,11 +8287,14 @@
         <v>646</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B155, $C$2:$C$777, C155, $D$2:$D$777, D155, $E$2:$E$777, E155) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+      <c r="O155" s="46" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="3">
         <v>46261.375</v>
       </c>
@@ -8330,11 +8336,11 @@
         <v>300</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B156, $C$2:$C$777, C156, $D$2:$D$777, D156, $E$2:$E$777, E156) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="157" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="3">
         <v>46274.375648148147</v>
       </c>
@@ -8376,11 +8382,11 @@
         <v>250</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B157, $C$2:$C$777, C157, $D$2:$D$777, D157, $E$2:$E$777, E157) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="158" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="11">
         <v>46252.6875</v>
       </c>
@@ -8412,11 +8418,11 @@
         <v>156</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B158, $C$2:$C$777, C158, $D$2:$D$777, D158, $E$2:$E$777, E158) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="8" t="s">
         <v>62</v>
       </c>
@@ -8448,11 +8454,11 @@
         <v>118</v>
       </c>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B159, $C$2:$C$777, C159, $D$2:$D$777, D159, $E$2:$E$777, E159) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="36">
         <v>46265.375694444447</v>
       </c>
@@ -8494,11 +8500,11 @@
         <v>294</v>
       </c>
       <c r="N160" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B160, $C$2:$C$777, C160, $D$2:$D$777, D160, $E$2:$E$777, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="161" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="36">
         <v>46266.375694444447</v>
       </c>
@@ -8540,11 +8546,11 @@
         <v>294</v>
       </c>
       <c r="N161" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B161, $C$2:$C$777, C161, $D$2:$D$777, D161, $E$2:$E$777, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="162" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="3">
         <v>46267.424305555556</v>
       </c>
@@ -8586,11 +8592,11 @@
         <v>280</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B162, $C$2:$C$777, C162, $D$2:$D$777, D162, $E$2:$E$777, E162) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="39">
         <v>46255</v>
       </c>
@@ -8632,12 +8638,12 @@
         <v>140</v>
       </c>
       <c r="N163" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B163, $C$2:$C$777, C163, $D$2:$D$777, D163, $E$2:$E$777, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O163" s="10"/>
     </row>
-    <row r="164" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="36">
         <v>46261.385416666664</v>
       </c>
@@ -8679,11 +8685,11 @@
         <v>300</v>
       </c>
       <c r="N164" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B164, $C$2:$C$777, C164, $D$2:$D$777, D164, $E$2:$E$777, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="165" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="57" t="s">
         <v>62</v>
       </c>
@@ -8718,7 +8724,7 @@
       <c r="L165" s="62"/>
       <c r="M165" s="62"/>
       <c r="N165" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B165, $C$2:$C$777, C165, $D$2:$D$777, D165, $E$2:$E$777, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O165" s="25"/>
@@ -8726,7 +8732,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="166" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -8768,12 +8774,12 @@
         <v>250</v>
       </c>
       <c r="N166" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B166, $C$2:$C$777, C166, $D$2:$D$777, D166, $E$2:$E$777, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P166" s="35"/>
     </row>
-    <row r="167" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -8815,11 +8821,11 @@
         <v>400</v>
       </c>
       <c r="N167" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B167, $C$2:$C$777, C167, $D$2:$D$777, D167, $E$2:$E$777, E167) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="168" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="36">
         <v>46267.461111111108</v>
       </c>
@@ -8861,13 +8867,13 @@
         <v>1000</v>
       </c>
       <c r="N168" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B168, $C$2:$C$777, C168, $D$2:$D$777, D168, $E$2:$E$777, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O168" s="26"/>
       <c r="P168" s="10"/>
     </row>
-    <row r="169" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="36">
         <v>46267.38958333333</v>
       </c>
@@ -8909,11 +8915,11 @@
         <v>700</v>
       </c>
       <c r="N169" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B169, $C$2:$C$777, C169, $D$2:$D$777, D169, $E$2:$E$777, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="170" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="11">
         <v>46252.6875</v>
       </c>
@@ -8945,11 +8951,11 @@
         <v>117</v>
       </c>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B170, $C$2:$C$777, C170, $D$2:$D$777, D170, $E$2:$E$777, E170) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="171" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="11">
         <v>46252.6875</v>
       </c>
@@ -8979,11 +8985,11 @@
       </c>
       <c r="J171" s="40"/>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B171, $C$2:$C$777, C171, $D$2:$D$777, D171, $E$2:$E$777, E171) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="172" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="3">
         <v>46266.509722222225</v>
       </c>
@@ -9021,15 +9027,15 @@
         <v>5820</v>
       </c>
       <c r="M172" s="18">
-        <f>ABS((D172*E172)-L172)</f>
+        <f t="shared" ref="M172:M177" si="9">ABS((D172*E172)-L172)</f>
         <v>300</v>
       </c>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B172, $C$2:$C$777, C172, $D$2:$D$777, D172, $E$2:$E$777, E172) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="173" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="3">
         <v>46265.474999999999</v>
       </c>
@@ -9067,15 +9073,15 @@
         <v>3810</v>
       </c>
       <c r="M173" s="18">
-        <f>ABS((D173*E173)-L173)</f>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N173" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B173, $C$2:$C$777, C173, $D$2:$D$777, D173, $E$2:$E$777, E173) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="174" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -9113,15 +9119,15 @@
         <v>7200</v>
       </c>
       <c r="M174" s="18">
-        <f>ABS((D174*E174)-L174)</f>
+        <f t="shared" si="9"/>
         <v>250</v>
       </c>
       <c r="N174" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B174, $C$2:$C$777, C174, $D$2:$D$777, D174, $E$2:$E$777, E174) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="175" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -9159,15 +9165,15 @@
         <v>4170</v>
       </c>
       <c r="M175" s="18">
-        <f>ABS((D175*E175)-L175)</f>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N175" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B175, $C$2:$C$777, C175, $D$2:$D$777, D175, $E$2:$E$777, E175) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="176" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="3">
         <v>46261.615277777775</v>
       </c>
@@ -9205,18 +9211,18 @@
         <v>10814</v>
       </c>
       <c r="M176" s="18">
-        <f>ABS((D176*E176)-L176)</f>
+        <f t="shared" si="9"/>
         <v>501</v>
       </c>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B176, $C$2:$C$777, C176, $D$2:$D$777, D176, $E$2:$E$777, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O176" s="46" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="177" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="3">
         <v>46267.375</v>
       </c>
@@ -9254,15 +9260,15 @@
         <v>16755</v>
       </c>
       <c r="M177" s="18">
-        <f>ABS((D177*E177)-L177)</f>
+        <f t="shared" si="9"/>
         <v>295</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B177, $C$2:$C$777, C177, $D$2:$D$777, D177, $E$2:$E$777, E177) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="178" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9292,11 +9298,11 @@
       </c>
       <c r="J178" s="40"/>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B178, $C$2:$C$777, C178, $D$2:$D$777, D178, $E$2:$E$777, E178) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="179" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="3">
         <v>46269.411111111112</v>
       </c>
@@ -9338,7 +9344,7 @@
         <v>650</v>
       </c>
       <c r="N179" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B179, $C$2:$C$777, C179, $D$2:$D$777, D179, $E$2:$E$777, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O179" s="46" t="s">
@@ -9346,7 +9352,7 @@
       </c>
       <c r="P179" s="10"/>
     </row>
-    <row r="180" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9378,14 +9384,14 @@
         <v>118</v>
       </c>
       <c r="N180" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B180, $C$2:$C$777, C180, $D$2:$D$777, D180, $E$2:$E$777, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="46" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="181" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9417,11 +9423,11 @@
         <v>117</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B181, $C$2:$C$777, C181, $D$2:$D$777, D181, $E$2:$E$777, E181) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="182" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="36">
         <v>46265.375694444447</v>
       </c>
@@ -9463,12 +9469,12 @@
         <v>300</v>
       </c>
       <c r="N182" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B182, $C$2:$C$777, C182, $D$2:$D$777, D182, $E$2:$E$777, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O182" s="35"/>
     </row>
-    <row r="183" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="54">
         <v>46243.505555555559</v>
       </c>
@@ -9510,12 +9516,12 @@
         <v>253</v>
       </c>
       <c r="N183" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B183, $C$2:$C$777, C183, $D$2:$D$777, D183, $E$2:$E$777, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="35"/>
     </row>
-    <row r="184" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="3">
         <v>46262.375</v>
       </c>
@@ -9557,11 +9563,11 @@
         <v>320</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B184, $C$2:$C$777, C184, $D$2:$D$777, D184, $E$2:$E$777, E184) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="185" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="3">
         <v>46265.486111111109</v>
       </c>
@@ -9603,11 +9609,11 @@
         <v>448</v>
       </c>
       <c r="N185" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B185, $C$2:$C$777, C185, $D$2:$D$777, D185, $E$2:$E$777, E185) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="186" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="3">
         <v>46262.375</v>
       </c>
@@ -9649,12 +9655,12 @@
         <v>370</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B186, $C$2:$C$777, C186, $D$2:$D$777, D186, $E$2:$E$777, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P186" s="35"/>
     </row>
-    <row r="187" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="8" t="s">
         <v>62</v>
       </c>
@@ -9686,11 +9692,11 @@
         <v>117</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B187, $C$2:$C$777, C187, $D$2:$D$777, D187, $E$2:$E$777, E187) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="188" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="8" t="s">
         <v>62</v>
       </c>
@@ -9720,11 +9726,11 @@
       </c>
       <c r="J188" s="40"/>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B188, $C$2:$C$777, C188, $D$2:$D$777, D188, $E$2:$E$777, E188) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="189" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="8" t="s">
         <v>62</v>
       </c>
@@ -9754,11 +9760,11 @@
       </c>
       <c r="J189" s="40"/>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B189, $C$2:$C$777, C189, $D$2:$D$777, D189, $E$2:$E$777, E189) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="190" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="11">
         <v>46252.6875</v>
       </c>
@@ -9786,15 +9792,15 @@
       <c r="I190" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J190" s="73" t="s">
+      <c r="J190" s="40" t="s">
         <v>117</v>
       </c>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B190, $C$2:$C$777, C190, $D$2:$D$777, D190, $E$2:$E$777, E190) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="191" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="3">
         <v>46272.451388888891</v>
       </c>
@@ -9836,11 +9842,11 @@
         <v>650</v>
       </c>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B191, $C$2:$C$777, C191, $D$2:$D$777, D191, $E$2:$E$777, E191) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="192" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="3">
         <v>46272.390972222223</v>
       </c>
@@ -9882,11 +9888,11 @@
         <v>934</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B192, $C$2:$C$777, C192, $D$2:$D$777, D192, $E$2:$E$777, E192) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="193" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="3">
         <v>46266.642361111109</v>
       </c>
@@ -9928,11 +9934,11 @@
         <v>500</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B193, $C$2:$C$777, C193, $D$2:$D$777, D193, $E$2:$E$777, E193) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="194" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -9974,7 +9980,7 @@
         <v>500</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B194, $C$2:$C$777, C194, $D$2:$D$777, D194, $E$2:$E$777, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="10">IF(COUNTIFS( $B$2:$B$777, B194, $C$2:$C$777, C194, $D$2:$D$777, D194, $E$2:$E$777, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O194" s="46" t="s">
@@ -9982,7 +9988,7 @@
       </c>
       <c r="P194" s="10"/>
     </row>
-    <row r="195" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="3">
         <v>46268.375</v>
       </c>
@@ -10024,13 +10030,13 @@
         <v>1800</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B195, $C$2:$C$777, C195, $D$2:$D$777, D195, $E$2:$E$777, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O195" s="10"/>
       <c r="P195" s="10"/>
     </row>
-    <row r="196" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -10060,11 +10066,11 @@
       </c>
       <c r="J196" s="40"/>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B196, $C$2:$C$777, C196, $D$2:$D$777, D196, $E$2:$E$777, E196) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="197" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="8" t="s">
         <v>62</v>
       </c>
@@ -10096,11 +10102,11 @@
         <v>201</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B197, $C$2:$C$777, C197, $D$2:$D$777, D197, $E$2:$E$777, E197) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="198" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="8" t="s">
         <v>62</v>
       </c>
@@ -10130,11 +10136,11 @@
       </c>
       <c r="J198" s="21"/>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B198, $C$2:$C$777, C198, $D$2:$D$777, D198, $E$2:$E$777, E198) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="199" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="3">
         <v>46258.443055555559</v>
       </c>
@@ -10176,11 +10182,11 @@
         <v>300</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B199, $C$2:$C$777, C199, $D$2:$D$777, D199, $E$2:$E$777, E199) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="200" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="3">
         <v>46259.375</v>
       </c>
@@ -10222,12 +10228,12 @@
         <v>188</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B200, $C$2:$C$777, C200, $D$2:$D$777, D200, $E$2:$E$777, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O200" s="10"/>
     </row>
-    <row r="201" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="8" t="s">
         <v>62</v>
       </c>
@@ -10259,11 +10265,11 @@
         <v>117</v>
       </c>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B201, $C$2:$C$777, C201, $D$2:$D$777, D201, $E$2:$E$777, E201) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="202" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -10305,11 +10311,11 @@
         <v>260</v>
       </c>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B202, $C$2:$C$777, C202, $D$2:$D$777, D202, $E$2:$E$777, E202) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="203" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="8" t="s">
         <v>62</v>
       </c>
@@ -10341,11 +10347,11 @@
         <v>118</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B203, $C$2:$C$777, C203, $D$2:$D$777, D203, $E$2:$E$777, E203) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="204" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="3">
         <v>46260.375</v>
       </c>
@@ -10387,7 +10393,7 @@
         <v>800</v>
       </c>
       <c r="N204" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B204, $C$2:$C$777, C204, $D$2:$D$777, D204, $E$2:$E$777, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10433,14 +10439,12 @@
         <v>268</v>
       </c>
       <c r="N205" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B205, $C$2:$C$777, C205, $D$2:$D$777, D205, $E$2:$E$777, E205) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O205" s="46" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="206" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+      <c r="O205" s="71"/>
+    </row>
+    <row r="206" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="36">
         <v>46258.443749999999</v>
       </c>
@@ -10482,13 +10486,13 @@
         <v>527.5</v>
       </c>
       <c r="N206" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B206, $C$2:$C$777, C206, $D$2:$D$777, D206, $E$2:$E$777, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O206" s="35"/>
       <c r="P206" s="35"/>
     </row>
-    <row r="207" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="54">
         <v>46253.4</v>
       </c>
@@ -10525,13 +10529,13 @@
       <c r="L207" s="33"/>
       <c r="M207" s="33"/>
       <c r="N207" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B207, $C$2:$C$777, C207, $D$2:$D$777, D207, $E$2:$E$777, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O207" s="35"/>
       <c r="P207" s="35"/>
     </row>
-    <row r="208" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="8" t="s">
         <v>62</v>
       </c>
@@ -10566,13 +10570,13 @@
       <c r="L208" s="18"/>
       <c r="M208" s="18"/>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B208, $C$2:$C$777, C208, $D$2:$D$777, D208, $E$2:$E$777, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O208" s="10"/>
       <c r="P208" s="10"/>
     </row>
-    <row r="209" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="8" t="s">
         <v>62</v>
       </c>
@@ -10602,11 +10606,11 @@
       </c>
       <c r="J209" s="40"/>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B209, $C$2:$C$777, C209, $D$2:$D$777, D209, $E$2:$E$777, E209) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="210" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="3">
         <v>46261.375</v>
       </c>
@@ -10648,12 +10652,12 @@
         <v>700</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B210, $C$2:$C$777, C210, $D$2:$D$777, D210, $E$2:$E$777, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O210" s="35"/>
     </row>
-    <row r="211" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="3">
         <v>46261.375</v>
       </c>
@@ -10695,11 +10699,11 @@
         <v>260</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B211, $C$2:$C$777, C211, $D$2:$D$777, D211, $E$2:$E$777, E211) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="212" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -10729,12 +10733,12 @@
       </c>
       <c r="J212" s="40"/>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B212, $C$2:$C$777, C212, $D$2:$D$777, D212, $E$2:$E$777, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P212" s="35"/>
     </row>
-    <row r="213" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="3">
         <v>46262.375</v>
       </c>
@@ -10776,13 +10780,13 @@
         <v>300</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B213, $C$2:$C$777, C213, $D$2:$D$777, D213, $E$2:$E$777, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O213" s="10"/>
       <c r="P213" s="10"/>
     </row>
-    <row r="214" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="3">
         <v>46261.375</v>
       </c>
@@ -10824,13 +10828,13 @@
         <v>300</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B214, $C$2:$C$777, C214, $D$2:$D$777, D214, $E$2:$E$777, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O214" s="10"/>
       <c r="P214" s="10"/>
     </row>
-    <row r="215" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="8" t="s">
         <v>62</v>
       </c>
@@ -10862,11 +10866,11 @@
         <v>118</v>
       </c>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B215, $C$2:$C$777, C215, $D$2:$D$777, D215, $E$2:$E$777, E215) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="216" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -10898,11 +10902,11 @@
         <v>117</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B216, $C$2:$C$777, C216, $D$2:$D$777, D216, $E$2:$E$777, E216) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="217" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="8" t="s">
         <v>62</v>
       </c>
@@ -10932,11 +10936,11 @@
       </c>
       <c r="J217" s="40"/>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B217, $C$2:$C$777, C217, $D$2:$D$777, D217, $E$2:$E$777, E217) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="218" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="11">
         <v>46253.375</v>
       </c>
@@ -10971,11 +10975,11 @@
         <v>144</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B218, $C$2:$C$777, C218, $D$2:$D$777, D218, $E$2:$E$777, E218) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="219" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="3">
         <v>46260.425694444442</v>
       </c>
@@ -11017,12 +11021,12 @@
         <v>1000</v>
       </c>
       <c r="N219" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B219, $C$2:$C$777, C219, $D$2:$D$777, D219, $E$2:$E$777, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P219" s="35"/>
     </row>
-    <row r="220" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="3">
         <v>46259.375</v>
       </c>
@@ -11064,12 +11068,12 @@
         <v>650</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B220, $C$2:$C$777, C220, $D$2:$D$777, D220, $E$2:$E$777, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O220" s="35"/>
     </row>
-    <row r="221" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="8" t="s">
         <v>62</v>
       </c>
@@ -11101,11 +11105,11 @@
         <v>118</v>
       </c>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B221, $C$2:$C$777, C221, $D$2:$D$777, D221, $E$2:$E$777, E221) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="222" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="8" t="s">
         <v>62</v>
       </c>
@@ -11135,11 +11139,11 @@
       </c>
       <c r="J222" s="40"/>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B222, $C$2:$C$777, C222, $D$2:$D$777, D222, $E$2:$E$777, E222) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="223" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="223" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="8" t="s">
         <v>62</v>
       </c>
@@ -11171,12 +11175,12 @@
         <v>118</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B223, $C$2:$C$777, C223, $D$2:$D$777, D223, $E$2:$E$777, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O223" s="35"/>
     </row>
-    <row r="224" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="9" t="s">
         <v>62</v>
       </c>
@@ -11206,7 +11210,7 @@
       </c>
       <c r="J224" s="40"/>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B224, $C$2:$C$777, C224, $D$2:$D$777, D224, $E$2:$E$777, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11252,11 +11256,11 @@
         <v>250</v>
       </c>
       <c r="N225" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B225, $C$2:$C$777, C225, $D$2:$D$777, D225, $E$2:$E$777, E225) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="226" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="8" t="s">
         <v>62</v>
       </c>
@@ -11288,11 +11292,11 @@
         <v>118</v>
       </c>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B226, $C$2:$C$777, C226, $D$2:$D$777, D226, $E$2:$E$777, E226) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="227" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="11">
         <v>46253.375</v>
       </c>
@@ -11327,11 +11331,11 @@
         <v>145</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B227, $C$2:$C$777, C227, $D$2:$D$777, D227, $E$2:$E$777, E227) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="228" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="228" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -11363,11 +11367,11 @@
         <v>55</v>
       </c>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B228, $C$2:$C$777, C228, $D$2:$D$777, D228, $E$2:$E$777, E228) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="229" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="3">
         <v>46259.388194444444</v>
       </c>
@@ -11409,11 +11413,11 @@
         <v>940</v>
       </c>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B229, $C$2:$C$777, C229, $D$2:$D$777, D229, $E$2:$E$777, E229) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="230" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="8" t="s">
         <v>62</v>
       </c>
@@ -11445,11 +11449,11 @@
         <v>118</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B230, $C$2:$C$777, C230, $D$2:$D$777, D230, $E$2:$E$777, E230) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="231" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="231" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="8" t="s">
         <v>62</v>
       </c>
@@ -11481,12 +11485,12 @@
         <v>117</v>
       </c>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B231, $C$2:$C$777, C231, $D$2:$D$777, D231, $E$2:$E$777, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P231" s="35"/>
     </row>
-    <row r="232" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="8" t="s">
         <v>62</v>
       </c>
@@ -11518,11 +11522,11 @@
         <v>117</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B232, $C$2:$C$777, C232, $D$2:$D$777, D232, $E$2:$E$777, E232) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="233" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="3">
         <v>46265.415277777778</v>
       </c>
@@ -11564,11 +11568,11 @@
         <v>285</v>
       </c>
       <c r="N233" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B233, $C$2:$C$777, C233, $D$2:$D$777, D233, $E$2:$E$777, E233) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="3">
         <v>46266.375</v>
       </c>
@@ -11610,11 +11614,11 @@
         <v>726</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B234, $C$2:$C$777, C234, $D$2:$D$777, D234, $E$2:$E$777, E234) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="3">
         <v>46260.375</v>
       </c>
@@ -11656,11 +11660,11 @@
         <v>300</v>
       </c>
       <c r="N235" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B235, $C$2:$C$777, C235, $D$2:$D$777, D235, $E$2:$E$777, E235) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="236" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="3">
         <v>46269.375</v>
       </c>
@@ -11702,13 +11706,13 @@
         <v>250</v>
       </c>
       <c r="N236" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B236, $C$2:$C$777, C236, $D$2:$D$777, D236, $E$2:$E$777, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O236" s="10"/>
       <c r="P236" s="10"/>
     </row>
-    <row r="237" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -11738,12 +11742,12 @@
       </c>
       <c r="J237" s="40"/>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B237, $C$2:$C$777, C237, $D$2:$D$777, D237, $E$2:$E$777, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O237" s="35"/>
     </row>
-    <row r="238" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="3">
         <v>46260.634027777778</v>
       </c>
@@ -11785,11 +11789,11 @@
         <v>480</v>
       </c>
       <c r="N238" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B238, $C$2:$C$777, C238, $D$2:$D$777, D238, $E$2:$E$777, E238) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="239" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -11824,11 +11828,11 @@
         <v>146</v>
       </c>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B239, $C$2:$C$777, C239, $D$2:$D$777, D239, $E$2:$E$777, E239) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="240" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="8" t="s">
         <v>62</v>
       </c>
@@ -11858,11 +11862,11 @@
       </c>
       <c r="J240" s="40"/>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B240, $C$2:$C$777, C240, $D$2:$D$777, D240, $E$2:$E$777, E240) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="241" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -11904,13 +11908,13 @@
         <v>275</v>
       </c>
       <c r="N241" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B241, $C$2:$C$777, C241, $D$2:$D$777, D241, $E$2:$E$777, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O241" s="10"/>
       <c r="P241" s="10"/>
     </row>
-    <row r="242" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -11940,11 +11944,11 @@
       </c>
       <c r="J242" s="40"/>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B242, $C$2:$C$777, C242, $D$2:$D$777, D242, $E$2:$E$777, E242) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="243" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="3">
         <v>46260.550694444442</v>
       </c>
@@ -11986,11 +11990,11 @@
         <v>300</v>
       </c>
       <c r="N243" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B243, $C$2:$C$777, C243, $D$2:$D$777, D243, $E$2:$E$777, E243) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="244" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="8" t="s">
         <v>62</v>
       </c>
@@ -12020,11 +12024,11 @@
       </c>
       <c r="J244" s="40"/>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B244, $C$2:$C$777, C244, $D$2:$D$777, D244, $E$2:$E$777, E244) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="245" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="8" t="s">
         <v>62</v>
       </c>
@@ -12056,11 +12060,11 @@
         <v>118</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B245, $C$2:$C$777, C245, $D$2:$D$777, D245, $E$2:$E$777, E245) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="246" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="3">
         <v>46260.375</v>
       </c>
@@ -12102,12 +12106,12 @@
         <v>650</v>
       </c>
       <c r="N246" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B246, $C$2:$C$777, C246, $D$2:$D$777, D246, $E$2:$E$777, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P246" s="35"/>
     </row>
-    <row r="247" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="8" t="s">
         <v>62</v>
       </c>
@@ -12137,11 +12141,11 @@
       </c>
       <c r="J247" s="40"/>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B247, $C$2:$C$777, C247, $D$2:$D$777, D247, $E$2:$E$777, E247) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="248" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="3">
         <v>46260.557638888888</v>
       </c>
@@ -12183,12 +12187,12 @@
         <v>250</v>
       </c>
       <c r="N248" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B248, $C$2:$C$777, C248, $D$2:$D$777, D248, $E$2:$E$777, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P248" s="35"/>
     </row>
-    <row r="249" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="20">
         <v>46255</v>
       </c>
@@ -12230,11 +12234,11 @@
         <v>300</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B249, $C$2:$C$777, C249, $D$2:$D$777, D249, $E$2:$E$777, E249) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="250" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="8" t="s">
         <v>62</v>
       </c>
@@ -12264,11 +12268,11 @@
       </c>
       <c r="J250" s="40"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B250, $C$2:$C$777, C250, $D$2:$D$777, D250, $E$2:$E$777, E250) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="251" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -12300,11 +12304,11 @@
         <v>118</v>
       </c>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B251, $C$2:$C$777, C251, $D$2:$D$777, D251, $E$2:$E$777, E251) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="252" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="8" t="s">
         <v>62</v>
       </c>
@@ -12334,11 +12338,11 @@
       </c>
       <c r="J252" s="40"/>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B252, $C$2:$C$777, C252, $D$2:$D$777, D252, $E$2:$E$777, E252) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="253" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="8" t="s">
         <v>62</v>
       </c>
@@ -12368,11 +12372,11 @@
       </c>
       <c r="J253" s="40"/>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B253, $C$2:$C$777, C253, $D$2:$D$777, D253, $E$2:$E$777, E253) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="254" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="11">
         <v>46252.6875</v>
       </c>
@@ -12404,12 +12408,12 @@
         <v>118</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B254, $C$2:$C$777, C254, $D$2:$D$777, D254, $E$2:$E$777, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O254" s="35"/>
     </row>
-    <row r="255" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="8" t="s">
         <v>62</v>
       </c>
@@ -12441,11 +12445,11 @@
         <v>118</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B255, $C$2:$C$777, C255, $D$2:$D$777, D255, $E$2:$E$777, E255) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="256" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="8" t="s">
         <v>62</v>
       </c>
@@ -12477,11 +12481,11 @@
         <v>117</v>
       </c>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B256, $C$2:$C$777, C256, $D$2:$D$777, D256, $E$2:$E$777, E256) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="257" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="8" t="s">
         <v>62</v>
       </c>
@@ -12511,12 +12515,12 @@
       </c>
       <c r="J257" s="40"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B257, $C$2:$C$777, C257, $D$2:$D$777, D257, $E$2:$E$777, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P257" s="35"/>
     </row>
-    <row r="258" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="8" t="s">
         <v>62</v>
       </c>
@@ -12546,11 +12550,11 @@
       </c>
       <c r="J258" s="40"/>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B258, $C$2:$C$777, C258, $D$2:$D$777, D258, $E$2:$E$777, E258) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="259" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="N258:N283" si="11">IF(COUNTIFS( $B$2:$B$777, B258, $C$2:$C$777, C258, $D$2:$D$777, D258, $E$2:$E$777, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="8" t="s">
         <v>62</v>
       </c>
@@ -12580,11 +12584,11 @@
       </c>
       <c r="J259" s="40"/>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B259, $C$2:$C$777, C259, $D$2:$D$777, D259, $E$2:$E$777, E259) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="260" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="8" t="s">
         <v>62</v>
       </c>
@@ -12617,13 +12621,13 @@
       <c r="L260" s="18"/>
       <c r="M260" s="18"/>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B260, $C$2:$C$777, C260, $D$2:$D$777, D260, $E$2:$E$777, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="10"/>
       <c r="P260" s="10"/>
     </row>
-    <row r="261" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="8" t="s">
         <v>62</v>
       </c>
@@ -12653,11 +12657,11 @@
       </c>
       <c r="J261" s="40"/>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B261, $C$2:$C$777, C261, $D$2:$D$777, D261, $E$2:$E$777, E261) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="262" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="8" t="s">
         <v>62</v>
       </c>
@@ -12687,11 +12691,11 @@
       </c>
       <c r="J262" s="40"/>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B262, $C$2:$C$777, C262, $D$2:$D$777, D262, $E$2:$E$777, E262) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="263" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="8" t="s">
         <v>62</v>
       </c>
@@ -12723,12 +12727,12 @@
         <v>118</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B263, $C$2:$C$777, C263, $D$2:$D$777, D263, $E$2:$E$777, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O263" s="35"/>
     </row>
-    <row r="264" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="8" t="s">
         <v>62</v>
       </c>
@@ -12758,11 +12762,11 @@
       </c>
       <c r="J264" s="40"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B264, $C$2:$C$777, C264, $D$2:$D$777, D264, $E$2:$E$777, E264) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="265" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="8" t="s">
         <v>62</v>
       </c>
@@ -12794,11 +12798,11 @@
         <v>118</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B265, $C$2:$C$777, C265, $D$2:$D$777, D265, $E$2:$E$777, E265) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="266" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="8" t="s">
         <v>62</v>
       </c>
@@ -12828,11 +12832,11 @@
       </c>
       <c r="J266" s="40"/>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B266, $C$2:$C$777, C266, $D$2:$D$777, D266, $E$2:$E$777, E266) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="267" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="8" t="s">
         <v>62</v>
       </c>
@@ -12862,11 +12866,11 @@
       </c>
       <c r="J267" s="40"/>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B267, $C$2:$C$777, C267, $D$2:$D$777, D267, $E$2:$E$777, E267) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="268" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="8" t="s">
         <v>62</v>
       </c>
@@ -12896,12 +12900,12 @@
       </c>
       <c r="J268" s="40"/>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B268, $C$2:$C$777, C268, $D$2:$D$777, D268, $E$2:$E$777, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O268" s="35"/>
     </row>
-    <row r="269" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="8" t="s">
         <v>62</v>
       </c>
@@ -12934,13 +12938,13 @@
       <c r="L269" s="18"/>
       <c r="M269" s="18"/>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B269, $C$2:$C$777, C269, $D$2:$D$777, D269, $E$2:$E$777, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O269" s="10"/>
       <c r="P269" s="10"/>
     </row>
-    <row r="270" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -12972,11 +12976,11 @@
         <v>55</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B270, $C$2:$C$777, C270, $D$2:$D$777, D270, $E$2:$E$777, E270) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="271" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="271" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="8" t="s">
         <v>62</v>
       </c>
@@ -13006,11 +13010,11 @@
       </c>
       <c r="J271" s="40"/>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B271, $C$2:$C$777, C271, $D$2:$D$777, D271, $E$2:$E$777, E271) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="272" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="272" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -13052,11 +13056,11 @@
         <v>250</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B272, $C$2:$C$777, C272, $D$2:$D$777, D272, $E$2:$E$777, E272) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="273" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="11">
         <v>46252.6875</v>
       </c>
@@ -13088,11 +13092,11 @@
         <v>118</v>
       </c>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B273, $C$2:$C$777, C273, $D$2:$D$777, D273, $E$2:$E$777, E273) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="274" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="274" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="8" t="s">
         <v>62</v>
       </c>
@@ -13124,11 +13128,11 @@
         <v>118</v>
       </c>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B274, $C$2:$C$777, C274, $D$2:$D$777, D274, $E$2:$E$777, E274) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="275" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="275" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="8" t="s">
         <v>62</v>
       </c>
@@ -13160,11 +13164,11 @@
         <v>118</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B275, $C$2:$C$777, C275, $D$2:$D$777, D275, $E$2:$E$777, E275) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="276" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="276" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="8" t="s">
         <v>62</v>
       </c>
@@ -13194,11 +13198,11 @@
       </c>
       <c r="J276" s="40"/>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B276, $C$2:$C$777, C276, $D$2:$D$777, D276, $E$2:$E$777, E276) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="277" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="277" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="8" t="s">
         <v>62</v>
       </c>
@@ -13228,12 +13232,12 @@
       </c>
       <c r="J277" s="40"/>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B277, $C$2:$C$777, C277, $D$2:$D$777, D277, $E$2:$E$777, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P277" s="35"/>
     </row>
-    <row r="278" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="3">
         <v>46259.532638888886</v>
       </c>
@@ -13275,11 +13279,11 @@
         <v>250</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B278, $C$2:$C$777, C278, $D$2:$D$777, D278, $E$2:$E$777, E278) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="279" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="8" t="s">
         <v>62</v>
       </c>
@@ -13309,11 +13313,11 @@
       </c>
       <c r="J279" s="40"/>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B279, $C$2:$C$777, C279, $D$2:$D$777, D279, $E$2:$E$777, E279) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="280" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="8" t="s">
         <v>62</v>
       </c>
@@ -13343,11 +13347,11 @@
       </c>
       <c r="J280" s="40"/>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B280, $C$2:$C$777, C280, $D$2:$D$777, D280, $E$2:$E$777, E280) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="281" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="8" t="s">
         <v>62</v>
       </c>
@@ -13377,11 +13381,11 @@
       </c>
       <c r="J281" s="40"/>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B281, $C$2:$C$777, C281, $D$2:$D$777, D281, $E$2:$E$777, E281) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="282" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="11">
         <v>46251.506249999999</v>
       </c>
@@ -13411,12 +13415,12 @@
       </c>
       <c r="J282" s="40"/>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B282, $C$2:$C$777, C282, $D$2:$D$777, D282, $E$2:$E$777, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O282" s="35"/>
     </row>
-    <row r="283" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="8" t="s">
         <v>62</v>
       </c>
@@ -13446,15 +13450,15 @@
       </c>
       <c r="J283" s="40"/>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$777, B283, $C$2:$C$777, C283, $D$2:$D$777, D283, $E$2:$E$777, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P283" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
+    <filterColumn colId="1">
       <filters>
-        <filter val="S"/>
+        <filter val="NETWEBEQ"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -13964,7 +13968,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B2, $C$2:$C$778, C2, $D$2:$D$778, D2, $E$2:$E$778, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$778, B2, $C$2:$C$778, C2, $D$2:$D$778, D2, $E$2:$E$778, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="26"/>
@@ -14005,7 +14009,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B3, $C$2:$C$778, C3, $D$2:$D$778, D3, $E$2:$E$778, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -14044,7 +14048,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B4, $C$2:$C$778, C4, $D$2:$D$778, D4, $E$2:$E$778, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -14083,7 +14087,7 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B5, $C$2:$C$778, C5, $D$2:$D$778, D5, $E$2:$E$778, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -14122,7 +14126,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B6, $C$2:$C$778, C6, $D$2:$D$778, D6, $E$2:$E$778, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="10"/>
@@ -14161,7 +14165,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B7, $C$2:$C$778, C7, $D$2:$D$778, D7, $E$2:$E$778, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="10"/>
@@ -14200,7 +14204,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B8, $C$2:$C$778, C8, $D$2:$D$778, D8, $E$2:$E$778, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="10"/>
@@ -14239,7 +14243,7 @@
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B9, $C$2:$C$778, C9, $D$2:$D$778, D9, $E$2:$E$778, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="19"/>
@@ -14280,7 +14284,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B10, $C$2:$C$778, C10, $D$2:$D$778, D10, $E$2:$E$778, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="10"/>
@@ -14328,7 +14332,7 @@
         <v>500</v>
       </c>
       <c r="N11" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B11, $C$2:$C$778, C11, $D$2:$D$778, D11, $E$2:$E$778, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="10"/>
@@ -14376,7 +14380,7 @@
         <v>300</v>
       </c>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B12, $C$2:$C$778, C12, $D$2:$D$778, D12, $E$2:$E$778, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="10"/>
@@ -14415,7 +14419,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B13, $C$2:$C$778, C13, $D$2:$D$778, D13, $E$2:$E$778, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="10"/>
@@ -14456,7 +14460,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B14, $C$2:$C$778, C14, $D$2:$D$778, D14, $E$2:$E$778, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14" s="10"/>
@@ -14495,7 +14499,7 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B15, $C$2:$C$778, C15, $D$2:$D$778, D15, $E$2:$E$778, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O15" s="10"/>
@@ -14543,7 +14547,7 @@
         <v>300</v>
       </c>
       <c r="N16" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B16, $C$2:$C$778, C16, $D$2:$D$778, D16, $E$2:$E$778, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16" s="25"/>
@@ -14587,7 +14591,7 @@
         <v>3156</v>
       </c>
       <c r="N17" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B17, $C$2:$C$778, C17, $D$2:$D$778, D17, $E$2:$E$778, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17" s="10"/>
@@ -14636,7 +14640,7 @@
         <v>650</v>
       </c>
       <c r="N18" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B18, $C$2:$C$778, C18, $D$2:$D$778, D18, $E$2:$E$778, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P18" s="10"/>
@@ -14674,7 +14678,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B19, $C$2:$C$778, C19, $D$2:$D$778, D19, $E$2:$E$778, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19" s="10"/>
@@ -14722,7 +14726,7 @@
         <v>450</v>
       </c>
       <c r="N20" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B20, $C$2:$C$778, C20, $D$2:$D$778, D20, $E$2:$E$778, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20" s="10"/>
@@ -14761,7 +14765,7 @@
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B21, $C$2:$C$778, C21, $D$2:$D$778, D21, $E$2:$E$778, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21" s="10"/>
@@ -14800,7 +14804,7 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B22, $C$2:$C$778, C22, $D$2:$D$778, D22, $E$2:$E$778, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22" s="10"/>
@@ -14841,7 +14845,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B23, $C$2:$C$778, C23, $D$2:$D$778, D23, $E$2:$E$778, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P23" s="10"/>
@@ -14881,7 +14885,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B24, $C$2:$C$778, C24, $D$2:$D$778, D24, $E$2:$E$778, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24" s="10"/>
@@ -14929,7 +14933,7 @@
         <v>516</v>
       </c>
       <c r="N25" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B25, $C$2:$C$778, C25, $D$2:$D$778, D25, $E$2:$E$778, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25" s="10"/>
@@ -14970,7 +14974,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B26, $C$2:$C$778, C26, $D$2:$D$778, D26, $E$2:$E$778, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P26" s="10"/>
@@ -15017,7 +15021,7 @@
         <v>300</v>
       </c>
       <c r="N27" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B27, $C$2:$C$778, C27, $D$2:$D$778, D27, $E$2:$E$778, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27" s="10"/>
@@ -15065,7 +15069,7 @@
         <v>222.75</v>
       </c>
       <c r="N28" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B28, $C$2:$C$778, C28, $D$2:$D$778, D28, $E$2:$E$778, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28" s="10"/>
@@ -15104,7 +15108,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B29, $C$2:$C$778, C29, $D$2:$D$778, D29, $E$2:$E$778, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29" s="10"/>
@@ -15143,7 +15147,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B30, $C$2:$C$778, C30, $D$2:$D$778, D30, $E$2:$E$778, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30" s="10"/>
@@ -15184,7 +15188,7 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B31, $C$2:$C$778, C31, $D$2:$D$778, D31, $E$2:$E$778, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31" s="10"/>
@@ -15223,7 +15227,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B32, $C$2:$C$778, C32, $D$2:$D$778, D32, $E$2:$E$778, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32" s="10"/>
@@ -15271,7 +15275,7 @@
         <v>300</v>
       </c>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B33, $C$2:$C$778, C33, $D$2:$D$778, D33, $E$2:$E$778, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33" s="10"/>
@@ -15319,7 +15323,7 @@
         <v>300</v>
       </c>
       <c r="N34" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B34, $C$2:$C$778, C34, $D$2:$D$778, D34, $E$2:$E$778, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34" s="10"/>
@@ -15358,7 +15362,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B35, $C$2:$C$778, C35, $D$2:$D$778, D35, $E$2:$E$778, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P35" s="10"/>
@@ -15405,7 +15409,7 @@
         <v>460</v>
       </c>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B36, $C$2:$C$778, C36, $D$2:$D$778, D36, $E$2:$E$778, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P36" s="10"/>
@@ -15443,7 +15447,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B37, $C$2:$C$778, C37, $D$2:$D$778, D37, $E$2:$E$778, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P37" s="10"/>
@@ -15481,7 +15485,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B38, $C$2:$C$778, C38, $D$2:$D$778, D38, $E$2:$E$778, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38" s="25"/>
@@ -15522,7 +15526,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B39, $C$2:$C$778, C39, $D$2:$D$778, D39, $E$2:$E$778, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39" s="10"/>
@@ -15562,7 +15566,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B40, $C$2:$C$778, C40, $D$2:$D$778, D40, $E$2:$E$778, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15601,7 +15605,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B41, $C$2:$C$778, C41, $D$2:$D$778, D41, $E$2:$E$778, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41" s="10"/>
@@ -15641,7 +15645,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B42, $C$2:$C$778, C42, $D$2:$D$778, D42, $E$2:$E$778, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15688,7 +15692,7 @@
         <v>540</v>
       </c>
       <c r="N43" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B43, $C$2:$C$778, C43, $D$2:$D$778, D43, $E$2:$E$778, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15734,7 +15738,7 @@
         <v>300</v>
       </c>
       <c r="N44" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B44, $C$2:$C$778, C44, $D$2:$D$778, D44, $E$2:$E$778, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15771,7 +15775,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B45, $C$2:$C$778, C45, $D$2:$D$778, D45, $E$2:$E$778, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45" s="34"/>
@@ -15811,7 +15815,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B46, $C$2:$C$778, C46, $D$2:$D$778, D46, $E$2:$E$778, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15850,7 +15854,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B47, $C$2:$C$778, C47, $D$2:$D$778, D47, $E$2:$E$778, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -15889,7 +15893,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B48, $C$2:$C$778, C48, $D$2:$D$778, D48, $E$2:$E$778, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48"/>
@@ -15928,7 +15932,7 @@
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
       <c r="N49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B49, $C$2:$C$778, C49, $D$2:$D$778, D49, $E$2:$E$778, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49"/>
@@ -15967,7 +15971,7 @@
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B50, $C$2:$C$778, C50, $D$2:$D$778, D50, $E$2:$E$778, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50"/>
@@ -16006,7 +16010,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B51, $C$2:$C$778, C51, $D$2:$D$778, D51, $E$2:$E$778, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51"/>
@@ -16045,7 +16049,7 @@
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B52, $C$2:$C$778, C52, $D$2:$D$778, D52, $E$2:$E$778, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52"/>
@@ -16084,7 +16088,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B53, $C$2:$C$778, C53, $D$2:$D$778, D53, $E$2:$E$778, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53"/>
@@ -16123,7 +16127,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B54, $C$2:$C$778, C54, $D$2:$D$778, D54, $E$2:$E$778, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
@@ -16162,7 +16166,7 @@
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B55, $C$2:$C$778, C55, $D$2:$D$778, D55, $E$2:$E$778, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -16201,7 +16205,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B56, $C$2:$C$778, C56, $D$2:$D$778, D56, $E$2:$E$778, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P56"/>
@@ -16239,7 +16243,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B57, $C$2:$C$778, C57, $D$2:$D$778, D57, $E$2:$E$778, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
@@ -16280,7 +16284,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B58, $C$2:$C$778, C58, $D$2:$D$778, D58, $E$2:$E$778, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
@@ -16328,7 +16332,7 @@
         <v>300</v>
       </c>
       <c r="N59" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B59, $C$2:$C$778, C59, $D$2:$D$778, D59, $E$2:$E$778, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59"/>
@@ -16367,7 +16371,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B60, $C$2:$C$778, C60, $D$2:$D$778, D60, $E$2:$E$778, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60"/>
@@ -16406,7 +16410,7 @@
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B61, $C$2:$C$778, C61, $D$2:$D$778, D61, $E$2:$E$778, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61"/>
@@ -16447,7 +16451,7 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B62, $C$2:$C$778, C62, $D$2:$D$778, D62, $E$2:$E$778, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62"/>
@@ -16488,7 +16492,7 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B63, $C$2:$C$778, C63, $D$2:$D$778, D63, $E$2:$E$778, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63"/>
@@ -16529,7 +16533,7 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B64, $C$2:$C$778, C64, $D$2:$D$778, D64, $E$2:$E$778, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
@@ -16568,7 +16572,7 @@
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B65, $C$2:$C$778, C65, $D$2:$D$778, D65, $E$2:$E$778, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65"/>
@@ -16609,7 +16613,7 @@
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B66, $C$2:$C$778, C66, $D$2:$D$778, D66, $E$2:$E$778, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$778, B66, $C$2:$C$778, C66, $D$2:$D$778, D66, $E$2:$E$778, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66"/>
@@ -16652,7 +16656,7 @@
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B67, $C$2:$C$778, C67, $D$2:$D$778, D67, $E$2:$E$778, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O67"/>
@@ -16691,7 +16695,7 @@
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B68, $C$2:$C$778, C68, $D$2:$D$778, D68, $E$2:$E$778, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68"/>
@@ -16739,7 +16743,7 @@
         <v>300</v>
       </c>
       <c r="N69" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B69, $C$2:$C$778, C69, $D$2:$D$778, D69, $E$2:$E$778, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69"/>
@@ -16778,7 +16782,7 @@
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B70, $C$2:$C$778, C70, $D$2:$D$778, D70, $E$2:$E$778, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70"/>
@@ -16819,7 +16823,7 @@
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B71, $C$2:$C$778, C71, $D$2:$D$778, D71, $E$2:$E$778, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O71"/>
@@ -16858,7 +16862,7 @@
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B72, $C$2:$C$778, C72, $D$2:$D$778, D72, $E$2:$E$778, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O72"/>
@@ -16897,7 +16901,7 @@
       <c r="L73" s="17"/>
       <c r="M73" s="17"/>
       <c r="N73" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B73, $C$2:$C$778, C73, $D$2:$D$778, D73, $E$2:$E$778, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O73"/>
@@ -16936,7 +16940,7 @@
       <c r="L74" s="17"/>
       <c r="M74" s="17"/>
       <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B74, $C$2:$C$778, C74, $D$2:$D$778, D74, $E$2:$E$778, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74"/>
@@ -16984,7 +16988,7 @@
         <v>442</v>
       </c>
       <c r="N75" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B75, $C$2:$C$778, C75, $D$2:$D$778, D75, $E$2:$E$778, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O75"/>
@@ -17025,7 +17029,7 @@
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B76, $C$2:$C$778, C76, $D$2:$D$778, D76, $E$2:$E$778, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O76"/>
@@ -17064,7 +17068,7 @@
       <c r="L77" s="17"/>
       <c r="M77" s="17"/>
       <c r="N77" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B77, $C$2:$C$778, C77, $D$2:$D$778, D77, $E$2:$E$778, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O77"/>
@@ -17103,7 +17107,7 @@
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B78, $C$2:$C$778, C78, $D$2:$D$778, D78, $E$2:$E$778, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78"/>
@@ -17144,7 +17148,7 @@
       <c r="L79" s="17"/>
       <c r="M79" s="17"/>
       <c r="N79" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B79, $C$2:$C$778, C79, $D$2:$D$778, D79, $E$2:$E$778, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O79"/>
@@ -17183,7 +17187,7 @@
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
       <c r="N80" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B80, $C$2:$C$778, C80, $D$2:$D$778, D80, $E$2:$E$778, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O80"/>
@@ -17222,7 +17226,7 @@
       <c r="L81" s="17"/>
       <c r="M81" s="17"/>
       <c r="N81" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B81, $C$2:$C$778, C81, $D$2:$D$778, D81, $E$2:$E$778, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O81"/>
@@ -17261,7 +17265,7 @@
       <c r="L82" s="17"/>
       <c r="M82" s="17"/>
       <c r="N82" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B82, $C$2:$C$778, C82, $D$2:$D$778, D82, $E$2:$E$778, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O82"/>
@@ -17300,7 +17304,7 @@
       <c r="L83" s="17"/>
       <c r="M83" s="17"/>
       <c r="N83" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B83, $C$2:$C$778, C83, $D$2:$D$778, D83, $E$2:$E$778, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O83"/>
@@ -17339,7 +17343,7 @@
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B84, $C$2:$C$778, C84, $D$2:$D$778, D84, $E$2:$E$778, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O84"/>
@@ -17378,7 +17382,7 @@
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B85, $C$2:$C$778, C85, $D$2:$D$778, D85, $E$2:$E$778, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O85"/>
@@ -17417,7 +17421,7 @@
       <c r="L86" s="17"/>
       <c r="M86" s="17"/>
       <c r="N86" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B86, $C$2:$C$778, C86, $D$2:$D$778, D86, $E$2:$E$778, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O86"/>
@@ -17456,7 +17460,7 @@
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
       <c r="N87" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B87, $C$2:$C$778, C87, $D$2:$D$778, D87, $E$2:$E$778, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O87"/>
@@ -17495,7 +17499,7 @@
       <c r="L88" s="17"/>
       <c r="M88" s="17"/>
       <c r="N88" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B88, $C$2:$C$778, C88, $D$2:$D$778, D88, $E$2:$E$778, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O88"/>
@@ -17536,7 +17540,7 @@
       <c r="L89" s="17"/>
       <c r="M89" s="17"/>
       <c r="N89" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B89, $C$2:$C$778, C89, $D$2:$D$778, D89, $E$2:$E$778, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O89"/>
@@ -17575,7 +17579,7 @@
       <c r="L90" s="17"/>
       <c r="M90" s="17"/>
       <c r="N90" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B90, $C$2:$C$778, C90, $D$2:$D$778, D90, $E$2:$E$778, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O90"/>
@@ -17614,7 +17618,7 @@
       <c r="L91" s="17"/>
       <c r="M91" s="17"/>
       <c r="N91" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B91, $C$2:$C$778, C91, $D$2:$D$778, D91, $E$2:$E$778, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O91"/>
@@ -17658,11 +17662,11 @@
         <v>8480</v>
       </c>
       <c r="M92" s="27">
-        <f t="shared" ref="M92:M101" si="0">ABS((D92*E92)-L92)</f>
+        <f t="shared" ref="M92:M101" si="2">ABS((D92*E92)-L92)</f>
         <v>280</v>
       </c>
       <c r="N92" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B92, $C$2:$C$778, C92, $D$2:$D$778, D92, $E$2:$E$778, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O92" s="46" t="s">
@@ -17707,11 +17711,11 @@
         <v>15050</v>
       </c>
       <c r="M93" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>430</v>
       </c>
       <c r="N93" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B93, $C$2:$C$778, C93, $D$2:$D$778, D93, $E$2:$E$778, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O93" s="46" t="s">
@@ -17756,11 +17760,11 @@
         <v>9170</v>
       </c>
       <c r="M94" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
       <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B94, $C$2:$C$778, C94, $D$2:$D$778, D94, $E$2:$E$778, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O94" s="46" t="s">
@@ -17805,11 +17809,11 @@
         <v>9170</v>
       </c>
       <c r="M95" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B95, $C$2:$C$778, C95, $D$2:$D$778, D95, $E$2:$E$778, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17851,11 +17855,11 @@
         <v>5755</v>
       </c>
       <c r="M96" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>275</v>
       </c>
       <c r="N96" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B96, $C$2:$C$778, C96, $D$2:$D$778, D96, $E$2:$E$778, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O96" s="46" t="s">
@@ -17900,11 +17904,11 @@
         <v>5805</v>
       </c>
       <c r="M97" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>225</v>
       </c>
       <c r="N97" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B97, $C$2:$C$778, C97, $D$2:$D$778, D97, $E$2:$E$778, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O97" s="46" t="s">
@@ -17949,11 +17953,11 @@
         <v>19730.5</v>
       </c>
       <c r="M98" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>504.5</v>
       </c>
       <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B98, $C$2:$C$778, C98, $D$2:$D$778, D98, $E$2:$E$778, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17995,11 +17999,11 @@
         <v>5940</v>
       </c>
       <c r="M99" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B99, $C$2:$C$778, C99, $D$2:$D$778, D99, $E$2:$E$778, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O99" s="46" t="s">
@@ -18044,11 +18048,11 @@
         <v>25300</v>
       </c>
       <c r="M100" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>650</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B100, $C$2:$C$778, C100, $D$2:$D$778, D100, $E$2:$E$778, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O100" s="46" t="s">
@@ -18093,11 +18097,11 @@
         <v>12480</v>
       </c>
       <c r="M101" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>495</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B101, $C$2:$C$778, C101, $D$2:$D$778, D101, $E$2:$E$778, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O101" s="46" t="s">
@@ -18139,7 +18143,7 @@
       <c r="L102" s="18"/>
       <c r="M102" s="18"/>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B102, $C$2:$C$778, C102, $D$2:$D$778, D102, $E$2:$E$778, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O102" s="46" t="s">
@@ -18188,7 +18192,7 @@
         <v>710.99999999999636</v>
       </c>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B103, $C$2:$C$778, C103, $D$2:$D$778, D103, $E$2:$E$778, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O103" s="10"/>
@@ -18235,7 +18239,7 @@
         <v>1567.5</v>
       </c>
       <c r="N104" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B104, $C$2:$C$778, C104, $D$2:$D$778, D104, $E$2:$E$778, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O104" s="46" t="s">
@@ -18284,7 +18288,7 @@
         <v>450</v>
       </c>
       <c r="N105" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B105, $C$2:$C$778, C105, $D$2:$D$778, D105, $E$2:$E$778, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O105" s="46" t="s">
@@ -18333,7 +18337,7 @@
         <v>300</v>
       </c>
       <c r="N106" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B106, $C$2:$C$778, C106, $D$2:$D$778, D106, $E$2:$E$778, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O106" s="46" t="s">
@@ -18373,7 +18377,7 @@
       <c r="L107" s="18"/>
       <c r="M107" s="18"/>
       <c r="N107" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B107, $C$2:$C$778, C107, $D$2:$D$778, D107, $E$2:$E$778, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="46" t="s">
@@ -18418,11 +18422,11 @@
         <v>25530</v>
       </c>
       <c r="M108" s="18">
-        <f t="shared" ref="M108:M117" si="1">ABS((D108*E108)-L108)</f>
+        <f t="shared" ref="M108:M117" si="3">ABS((D108*E108)-L108)</f>
         <v>650</v>
       </c>
       <c r="N108" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B108, $C$2:$C$778, C108, $D$2:$D$778, D108, $E$2:$E$778, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18464,11 +18468,11 @@
         <v>3560</v>
       </c>
       <c r="M109" s="33">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+      <c r="N109" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>175</v>
-      </c>
-      <c r="N109" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B109, $C$2:$C$778, C109, $D$2:$D$778, D109, $E$2:$E$778, E109) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O109" s="46" t="s">
@@ -18513,11 +18517,11 @@
         <v>3510</v>
       </c>
       <c r="M110" s="33">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+      <c r="N110" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>225</v>
-      </c>
-      <c r="N110" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B110, $C$2:$C$778, C110, $D$2:$D$778, D110, $E$2:$E$778, E110) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O110" s="46" t="s">
@@ -18562,11 +18566,11 @@
         <v>8810</v>
       </c>
       <c r="M111" s="18">
+        <f t="shared" si="3"/>
+        <v>650</v>
+      </c>
+      <c r="N111" t="str">
         <f t="shared" si="1"/>
-        <v>650</v>
-      </c>
-      <c r="N111" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B111, $C$2:$C$778, C111, $D$2:$D$778, D111, $E$2:$E$778, E111) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O111" s="46" t="s">
@@ -18611,11 +18615,11 @@
         <v>20260</v>
       </c>
       <c r="M112" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N112" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N112" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B112, $C$2:$C$778, C112, $D$2:$D$778, D112, $E$2:$E$778, E112) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O112"/>
@@ -18658,11 +18662,11 @@
         <v>16219.999999999998</v>
       </c>
       <c r="M113" s="33">
+        <f t="shared" si="3"/>
+        <v>300.00000000000182</v>
+      </c>
+      <c r="N113" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>300.00000000000182</v>
-      </c>
-      <c r="N113" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B113, $C$2:$C$778, C113, $D$2:$D$778, D113, $E$2:$E$778, E113) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O113" s="46" t="s">
@@ -18707,11 +18711,11 @@
         <v>6334</v>
       </c>
       <c r="M114" s="33">
+        <f t="shared" si="3"/>
+        <v>274</v>
+      </c>
+      <c r="N114" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="N114" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B114, $C$2:$C$778, C114, $D$2:$D$778, D114, $E$2:$E$778, E114) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O114" s="46" t="s">
@@ -18756,11 +18760,11 @@
         <v>12510</v>
       </c>
       <c r="M115" s="18">
+        <f t="shared" si="3"/>
+        <v>290</v>
+      </c>
+      <c r="N115" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>290</v>
-      </c>
-      <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B115, $C$2:$C$778, C115, $D$2:$D$778, D115, $E$2:$E$778, E115) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -18802,11 +18806,11 @@
         <v>9270</v>
       </c>
       <c r="M116" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N116" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B116, $C$2:$C$778, C116, $D$2:$D$778, D116, $E$2:$E$778, E116) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O116" s="10"/>
@@ -18849,11 +18853,11 @@
         <v>5620</v>
       </c>
       <c r="M117" s="33">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N117" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B117, $C$2:$C$778, C117, $D$2:$D$778, D117, $E$2:$E$778, E117) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O117" s="10"/>
@@ -18888,7 +18892,7 @@
       </c>
       <c r="J118" s="40"/>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B118, $C$2:$C$778, C118, $D$2:$D$778, D118, $E$2:$E$778, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18930,11 +18934,11 @@
         <v>15075</v>
       </c>
       <c r="M119" s="18">
-        <f t="shared" ref="M119:M129" si="2">ABS((D119*E119)-L119)</f>
+        <f t="shared" ref="M119:M129" si="4">ABS((D119*E119)-L119)</f>
         <v>645</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B119, $C$2:$C$778, C119, $D$2:$D$778, D119, $E$2:$E$778, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18976,11 +18980,11 @@
         <v>16580</v>
       </c>
       <c r="M120" s="62">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>750</v>
       </c>
       <c r="N120" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B120, $C$2:$C$778, C120, $D$2:$D$778, D120, $E$2:$E$778, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P120" s="25" t="s">
@@ -19025,11 +19029,11 @@
         <v>8220</v>
       </c>
       <c r="M121" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>360</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B121, $C$2:$C$778, C121, $D$2:$D$778, D121, $E$2:$E$778, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="46" t="s">
@@ -19074,11 +19078,11 @@
         <v>26020</v>
       </c>
       <c r="M122" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>340</v>
       </c>
       <c r="N122" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B122, $C$2:$C$778, C122, $D$2:$D$778, D122, $E$2:$E$778, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19120,11 +19124,11 @@
         <v>4080</v>
       </c>
       <c r="M123" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B123, $C$2:$C$778, C123, $D$2:$D$778, D123, $E$2:$E$778, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19166,11 +19170,11 @@
         <v>5905</v>
       </c>
       <c r="M124" s="62">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>275</v>
       </c>
       <c r="N124" s="64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B124, $C$2:$C$778, C124, $D$2:$D$778, D124, $E$2:$E$778, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P124" s="25" t="s">
@@ -19215,11 +19219,11 @@
         <v>26180</v>
       </c>
       <c r="M125" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B125, $C$2:$C$778, C125, $D$2:$D$778, D125, $E$2:$E$778, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19261,11 +19265,11 @@
         <v>32200</v>
       </c>
       <c r="M126" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1200</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B126, $C$2:$C$778, C126, $D$2:$D$778, D126, $E$2:$E$778, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19307,11 +19311,11 @@
         <v>12600</v>
       </c>
       <c r="M127" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>360</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B127, $C$2:$C$778, C127, $D$2:$D$778, D127, $E$2:$E$778, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19353,11 +19357,11 @@
         <v>3005</v>
       </c>
       <c r="M128" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>240</v>
       </c>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B128, $C$2:$C$778, C128, $D$2:$D$778, D128, $E$2:$E$778, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="10"/>
@@ -19400,11 +19404,11 @@
         <v>26300</v>
       </c>
       <c r="M129" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B129, $C$2:$C$778, C129, $D$2:$D$778, D129, $E$2:$E$778, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19438,7 +19442,7 @@
       </c>
       <c r="J130" s="40"/>
       <c r="N130" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B130, $C$2:$C$778, C130, $D$2:$D$778, D130, $E$2:$E$778, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="5">IF(COUNTIFS( $B$2:$B$778, B130, $C$2:$C$778, C130, $D$2:$D$778, D130, $E$2:$E$778, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="25"/>
@@ -19485,7 +19489,7 @@
         <v>300</v>
       </c>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B131, $C$2:$C$778, C131, $D$2:$D$778, D131, $E$2:$E$778, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O131" s="10"/>
@@ -19532,7 +19536,7 @@
         <v>300</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B132, $C$2:$C$778, C132, $D$2:$D$778, D132, $E$2:$E$778, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O132" s="46" t="s">
@@ -19581,7 +19585,7 @@
         <v>300</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B133, $C$2:$C$778, C133, $D$2:$D$778, D133, $E$2:$E$778, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O133"/>
@@ -19618,7 +19622,7 @@
         <v>118</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B134, $C$2:$C$778, C134, $D$2:$D$778, D134, $E$2:$E$778, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="46" t="s">
@@ -19662,7 +19666,7 @@
       <c r="L135" s="17"/>
       <c r="M135" s="17"/>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B135, $C$2:$C$778, C135, $D$2:$D$778, D135, $E$2:$E$778, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19708,7 +19712,7 @@
         <v>150</v>
       </c>
       <c r="N136" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B136, $C$2:$C$778, C136, $D$2:$D$778, D136, $E$2:$E$778, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -19754,7 +19758,7 @@
         <v>250</v>
       </c>
       <c r="N137" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B137, $C$2:$C$778, C137, $D$2:$D$778, D137, $E$2:$E$778, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -19800,7 +19804,7 @@
         <v>300</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B138, $C$2:$C$778, C138, $D$2:$D$778, D138, $E$2:$E$778, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19846,7 +19850,7 @@
         <v>500</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B139, $C$2:$C$778, C139, $D$2:$D$778, D139, $E$2:$E$778, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O139" s="47" t="s">
@@ -19883,7 +19887,7 @@
       </c>
       <c r="J140" s="40"/>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B140, $C$2:$C$778, C140, $D$2:$D$778, D140, $E$2:$E$778, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19929,7 +19933,7 @@
         <v>270</v>
       </c>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B141, $C$2:$C$778, C141, $D$2:$D$778, D141, $E$2:$E$778, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O141" s="47" t="s">
@@ -19978,7 +19982,7 @@
         <v>300</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B142, $C$2:$C$778, C142, $D$2:$D$778, D142, $E$2:$E$778, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20017,7 +20021,7 @@
       <c r="L143" s="62"/>
       <c r="M143" s="62"/>
       <c r="N143" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B143, $C$2:$C$778, C143, $D$2:$D$778, D143, $E$2:$E$778, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P143" s="25" t="s">
@@ -20066,7 +20070,7 @@
         <v>300</v>
       </c>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B144, $C$2:$C$778, C144, $D$2:$D$778, D144, $E$2:$E$778, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O144" s="35"/>
@@ -20113,7 +20117,7 @@
         <v>1000</v>
       </c>
       <c r="N145" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B145, $C$2:$C$778, C145, $D$2:$D$778, D145, $E$2:$E$778, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O145" s="26"/>
@@ -20160,7 +20164,7 @@
         <v>700</v>
       </c>
       <c r="N146" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B146, $C$2:$C$778, C146, $D$2:$D$778, D146, $E$2:$E$778, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -20206,7 +20210,7 @@
         <v>250</v>
       </c>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B147, $C$2:$C$778, C147, $D$2:$D$778, D147, $E$2:$E$778, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20252,7 +20256,7 @@
         <v>300</v>
       </c>
       <c r="N148" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B148, $C$2:$C$778, C148, $D$2:$D$778, D148, $E$2:$E$778, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20288,7 +20292,7 @@
         <v>156</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B149, $C$2:$C$778, C149, $D$2:$D$778, D149, $E$2:$E$778, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20334,7 +20338,7 @@
         <v>650</v>
       </c>
       <c r="N150" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B150, $C$2:$C$778, C150, $D$2:$D$778, D150, $E$2:$E$778, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O150" s="46" t="s">
@@ -20383,7 +20387,7 @@
         <v>268</v>
       </c>
       <c r="N151" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B151, $C$2:$C$778, C151, $D$2:$D$778, D151, $E$2:$E$778, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O151" s="46" t="s">
@@ -20432,7 +20436,7 @@
         <v>400</v>
       </c>
       <c r="N152" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B152, $C$2:$C$778, C152, $D$2:$D$778, D152, $E$2:$E$778, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20478,7 +20482,7 @@
         <v>295</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B153, $C$2:$C$778, C153, $D$2:$D$778, D153, $E$2:$E$778, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20512,7 +20516,7 @@
       </c>
       <c r="J154" s="40"/>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B154, $C$2:$C$778, C154, $D$2:$D$778, D154, $E$2:$E$778, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20548,7 +20552,7 @@
         <v>118</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B155, $C$2:$C$778, C155, $D$2:$D$778, D155, $E$2:$E$778, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20584,7 +20588,7 @@
         <v>117</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B156, $C$2:$C$778, C156, $D$2:$D$778, D156, $E$2:$E$778, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20630,7 +20634,7 @@
         <v>300</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B157, $C$2:$C$778, C157, $D$2:$D$778, D157, $E$2:$E$778, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20676,7 +20680,7 @@
         <v>294</v>
       </c>
       <c r="N158" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B158, $C$2:$C$778, C158, $D$2:$D$778, D158, $E$2:$E$778, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -20722,7 +20726,7 @@
         <v>294</v>
       </c>
       <c r="N159" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B159, $C$2:$C$778, C159, $D$2:$D$778, D159, $E$2:$E$778, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -20768,7 +20772,7 @@
         <v>280</v>
       </c>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B160, $C$2:$C$778, C160, $D$2:$D$778, D160, $E$2:$E$778, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20814,7 +20818,7 @@
         <v>300</v>
       </c>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B161, $C$2:$C$778, C161, $D$2:$D$778, D161, $E$2:$E$778, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20848,7 +20852,7 @@
       </c>
       <c r="J162" s="40"/>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B162, $C$2:$C$778, C162, $D$2:$D$778, D162, $E$2:$E$778, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20894,7 +20898,7 @@
         <v>250</v>
       </c>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B163, $C$2:$C$778, C163, $D$2:$D$778, D163, $E$2:$E$778, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O163" s="10"/>
@@ -20941,7 +20945,7 @@
         <v>260</v>
       </c>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B164, $C$2:$C$778, C164, $D$2:$D$778, D164, $E$2:$E$778, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20987,7 +20991,7 @@
         <v>500</v>
       </c>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B165, $C$2:$C$778, C165, $D$2:$D$778, D165, $E$2:$E$778, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21023,7 +21027,7 @@
         <v>117</v>
       </c>
       <c r="N166" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B166, $C$2:$C$778, C166, $D$2:$D$778, D166, $E$2:$E$778, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21057,7 +21061,7 @@
       </c>
       <c r="J167" s="40"/>
       <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B167, $C$2:$C$778, C167, $D$2:$D$778, D167, $E$2:$E$778, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21103,7 +21107,7 @@
         <v>370</v>
       </c>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B168, $C$2:$C$778, C168, $D$2:$D$778, D168, $E$2:$E$778, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O168" s="10"/>
@@ -21150,7 +21154,7 @@
         <v>320</v>
       </c>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B169, $C$2:$C$778, C169, $D$2:$D$778, D169, $E$2:$E$778, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21196,7 +21200,7 @@
         <v>448</v>
       </c>
       <c r="N170" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B170, $C$2:$C$778, C170, $D$2:$D$778, D170, $E$2:$E$778, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21232,7 +21236,7 @@
         <v>201</v>
       </c>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B171, $C$2:$C$778, C171, $D$2:$D$778, D171, $E$2:$E$778, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21274,11 +21278,11 @@
         <v>5290</v>
       </c>
       <c r="M172" s="18">
-        <f t="shared" ref="M172:M180" si="3">ABS((D172*E172)-L172)</f>
+        <f t="shared" ref="M172:M180" si="6">ABS((D172*E172)-L172)</f>
         <v>250</v>
       </c>
       <c r="N172" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B172, $C$2:$C$778, C172, $D$2:$D$778, D172, $E$2:$E$778, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21320,11 +21324,11 @@
         <v>18140</v>
       </c>
       <c r="M173" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
       <c r="N173" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B173, $C$2:$C$778, C173, $D$2:$D$778, D173, $E$2:$E$778, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O173" s="46" t="s">
@@ -21369,11 +21373,11 @@
         <v>17040</v>
       </c>
       <c r="M174" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>880</v>
       </c>
       <c r="N174" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B174, $C$2:$C$778, C174, $D$2:$D$778, D174, $E$2:$E$778, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21415,11 +21419,11 @@
         <v>5520</v>
       </c>
       <c r="M175" s="33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N175" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B175, $C$2:$C$778, C175, $D$2:$D$778, D175, $E$2:$E$778, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O175" s="35"/>
@@ -21462,11 +21466,11 @@
         <v>2657</v>
       </c>
       <c r="M176" s="33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>253</v>
       </c>
       <c r="N176" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B176, $C$2:$C$778, C176, $D$2:$D$778, D176, $E$2:$E$778, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O176" s="35"/>
@@ -21509,11 +21513,11 @@
         <v>3810</v>
       </c>
       <c r="M177" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N177" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B177, $C$2:$C$778, C177, $D$2:$D$778, D177, $E$2:$E$778, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21555,11 +21559,11 @@
         <v>9312.5</v>
       </c>
       <c r="M178" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B178, $C$2:$C$778, C178, $D$2:$D$778, D178, $E$2:$E$778, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O178" s="46" t="s">
@@ -21604,11 +21608,11 @@
         <v>4680</v>
       </c>
       <c r="M179" s="33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>140</v>
       </c>
       <c r="N179" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B179, $C$2:$C$778, C179, $D$2:$D$778, D179, $E$2:$E$778, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O179" s="10"/>
@@ -21651,11 +21655,11 @@
         <v>4520</v>
       </c>
       <c r="M180" s="33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N180" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B180, $C$2:$C$778, C180, $D$2:$D$778, D180, $E$2:$E$778, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -21689,7 +21693,7 @@
       </c>
       <c r="J181" s="40"/>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B181, $C$2:$C$778, C181, $D$2:$D$778, D181, $E$2:$E$778, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O181" s="35"/>
@@ -21726,7 +21730,7 @@
         <v>118</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B182, $C$2:$C$778, C182, $D$2:$D$778, D182, $E$2:$E$778, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O182" s="46" t="s">
@@ -21765,7 +21769,7 @@
         <v>117</v>
       </c>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B183, $C$2:$C$778, C183, $D$2:$D$778, D183, $E$2:$E$778, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21811,7 +21815,7 @@
         <v>700</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B184, $C$2:$C$778, C184, $D$2:$D$778, D184, $E$2:$E$778, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O184" s="35"/>
@@ -21858,7 +21862,7 @@
         <v>501</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B185, $C$2:$C$778, C185, $D$2:$D$778, D185, $E$2:$E$778, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O185" s="46" t="s">
@@ -21897,7 +21901,7 @@
         <v>118</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B186, $C$2:$C$778, C186, $D$2:$D$778, D186, $E$2:$E$778, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21943,7 +21947,7 @@
         <v>300</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B187, $C$2:$C$778, C187, $D$2:$D$778, D187, $E$2:$E$778, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21977,7 +21981,7 @@
       </c>
       <c r="J188" s="40"/>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B188, $C$2:$C$778, C188, $D$2:$D$778, D188, $E$2:$E$778, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22011,7 +22015,7 @@
       </c>
       <c r="J189" s="40"/>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B189, $C$2:$C$778, C189, $D$2:$D$778, D189, $E$2:$E$778, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22057,7 +22061,7 @@
         <v>650</v>
       </c>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B190, $C$2:$C$778, C190, $D$2:$D$778, D190, $E$2:$E$778, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22103,7 +22107,7 @@
         <v>934</v>
       </c>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B191, $C$2:$C$778, C191, $D$2:$D$778, D191, $E$2:$E$778, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22137,7 +22141,7 @@
       </c>
       <c r="J192" s="40"/>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B192, $C$2:$C$778, C192, $D$2:$D$778, D192, $E$2:$E$778, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22183,7 +22187,7 @@
         <v>1800</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B193, $C$2:$C$778, C193, $D$2:$D$778, D193, $E$2:$E$778, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22229,7 +22233,7 @@
         <v>527.5</v>
       </c>
       <c r="N194" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B194, $C$2:$C$778, C194, $D$2:$D$778, D194, $E$2:$E$778, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="7">IF(COUNTIFS( $B$2:$B$778, B194, $C$2:$C$778, C194, $D$2:$D$778, D194, $E$2:$E$778, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -22270,7 +22274,7 @@
       <c r="L195" s="33"/>
       <c r="M195" s="33"/>
       <c r="N195" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B195, $C$2:$C$778, C195, $D$2:$D$778, D195, $E$2:$E$778, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22316,7 +22320,7 @@
         <v>260</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B196, $C$2:$C$778, C196, $D$2:$D$778, D196, $E$2:$E$778, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22352,7 +22356,7 @@
         <v>117</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B197, $C$2:$C$778, C197, $D$2:$D$778, D197, $E$2:$E$778, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22388,7 +22392,7 @@
         <v>117</v>
       </c>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B198, $C$2:$C$778, C198, $D$2:$D$778, D198, $E$2:$E$778, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22434,7 +22438,7 @@
         <v>300</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B199, $C$2:$C$778, C199, $D$2:$D$778, D199, $E$2:$E$778, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22471,7 +22475,7 @@
       <c r="L200" s="18"/>
       <c r="M200" s="18"/>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B200, $C$2:$C$778, C200, $D$2:$D$778, D200, $E$2:$E$778, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O200" s="10"/>
@@ -22511,7 +22515,7 @@
         <v>144</v>
       </c>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B201, $C$2:$C$778, C201, $D$2:$D$778, D201, $E$2:$E$778, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22545,7 +22549,7 @@
       </c>
       <c r="J202" s="40"/>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B202, $C$2:$C$778, C202, $D$2:$D$778, D202, $E$2:$E$778, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22579,7 +22583,7 @@
       </c>
       <c r="J203" s="40"/>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B203, $C$2:$C$778, C203, $D$2:$D$778, D203, $E$2:$E$778, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22615,7 +22619,7 @@
         <v>118</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B204, $C$2:$C$778, C204, $D$2:$D$778, D204, $E$2:$E$778, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O204" s="35"/>
@@ -22655,7 +22659,7 @@
         <v>145</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B205, $C$2:$C$778, C205, $D$2:$D$778, D205, $E$2:$E$778, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22689,7 +22693,7 @@
       </c>
       <c r="J206" s="40"/>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B206, $C$2:$C$778, C206, $D$2:$D$778, D206, $E$2:$E$778, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22735,7 +22739,7 @@
         <v>300</v>
       </c>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B207, $C$2:$C$778, C207, $D$2:$D$778, D207, $E$2:$E$778, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22781,7 +22785,7 @@
         <v>188</v>
       </c>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B208, $C$2:$C$778, C208, $D$2:$D$778, D208, $E$2:$E$778, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O208" s="10"/>
@@ -22818,7 +22822,7 @@
         <v>55</v>
       </c>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B209, $C$2:$C$778, C209, $D$2:$D$778, D209, $E$2:$E$778, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22854,7 +22858,7 @@
         <v>118</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B210, $C$2:$C$778, C210, $D$2:$D$778, D210, $E$2:$E$778, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22890,7 +22894,7 @@
         <v>118</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B211, $C$2:$C$778, C211, $D$2:$D$778, D211, $E$2:$E$778, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22926,7 +22930,7 @@
         <v>117</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B212, $C$2:$C$778, C212, $D$2:$D$778, D212, $E$2:$E$778, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22972,7 +22976,7 @@
         <v>1000</v>
       </c>
       <c r="N213" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B213, $C$2:$C$778, C213, $D$2:$D$778, D213, $E$2:$E$778, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O213" s="10"/>
@@ -23012,7 +23016,7 @@
       <c r="L214" s="18"/>
       <c r="M214" s="18"/>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B214, $C$2:$C$778, C214, $D$2:$D$778, D214, $E$2:$E$778, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O214" s="10"/>
@@ -23049,7 +23053,7 @@
         <v>117</v>
       </c>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B215, $C$2:$C$778, C215, $D$2:$D$778, D215, $E$2:$E$778, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23083,7 +23087,7 @@
       </c>
       <c r="J216" s="40"/>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B216, $C$2:$C$778, C216, $D$2:$D$778, D216, $E$2:$E$778, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O216" s="35"/>
@@ -23120,7 +23124,7 @@
         <v>117</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B217, $C$2:$C$778, C217, $D$2:$D$778, D217, $E$2:$E$778, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23154,7 +23158,7 @@
       </c>
       <c r="J218" s="40"/>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B218, $C$2:$C$778, C218, $D$2:$D$778, D218, $E$2:$E$778, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23190,7 +23194,7 @@
         <v>118</v>
       </c>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B219, $C$2:$C$778, C219, $D$2:$D$778, D219, $E$2:$E$778, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23226,7 +23230,7 @@
         <v>118</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B220, $C$2:$C$778, C220, $D$2:$D$778, D220, $E$2:$E$778, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23272,7 +23276,7 @@
         <v>300</v>
       </c>
       <c r="N221" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B221, $C$2:$C$778, C221, $D$2:$D$778, D221, $E$2:$E$778, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23318,7 +23322,7 @@
         <v>250</v>
       </c>
       <c r="N222" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B222, $C$2:$C$778, C222, $D$2:$D$778, D222, $E$2:$E$778, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23364,7 +23368,7 @@
         <v>940</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B223, $C$2:$C$778, C223, $D$2:$D$778, D223, $E$2:$E$778, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23410,7 +23414,7 @@
         <v>285</v>
       </c>
       <c r="N224" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B224, $C$2:$C$778, C224, $D$2:$D$778, D224, $E$2:$E$778, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23456,7 +23460,7 @@
         <v>726</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B225, $C$2:$C$778, C225, $D$2:$D$778, D225, $E$2:$E$778, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23490,7 +23494,7 @@
       </c>
       <c r="J226" s="40"/>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B226, $C$2:$C$778, C226, $D$2:$D$778, D226, $E$2:$E$778, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23526,7 +23530,7 @@
         <v>55</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B227, $C$2:$C$778, C227, $D$2:$D$778, D227, $E$2:$E$778, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23572,7 +23576,7 @@
         <v>300</v>
       </c>
       <c r="N228" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B228, $C$2:$C$778, C228, $D$2:$D$778, D228, $E$2:$E$778, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23608,7 +23612,7 @@
         <v>118</v>
       </c>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B229, $C$2:$C$778, C229, $D$2:$D$778, D229, $E$2:$E$778, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23654,7 +23658,7 @@
         <v>800</v>
       </c>
       <c r="N230" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B230, $C$2:$C$778, C230, $D$2:$D$778, D230, $E$2:$E$778, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23690,7 +23694,7 @@
         <v>118</v>
       </c>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B231, $C$2:$C$778, C231, $D$2:$D$778, D231, $E$2:$E$778, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23736,7 +23740,7 @@
         <v>650</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B232, $C$2:$C$778, C232, $D$2:$D$778, D232, $E$2:$E$778, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O232" s="35"/>
@@ -23783,7 +23787,7 @@
         <v>275</v>
       </c>
       <c r="N233" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B233, $C$2:$C$778, C233, $D$2:$D$778, D233, $E$2:$E$778, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23822,7 +23826,7 @@
         <v>146</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B234, $C$2:$C$778, C234, $D$2:$D$778, D234, $E$2:$E$778, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23868,7 +23872,7 @@
         <v>480</v>
       </c>
       <c r="N235" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B235, $C$2:$C$778, C235, $D$2:$D$778, D235, $E$2:$E$778, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23914,7 +23918,7 @@
         <v>650</v>
       </c>
       <c r="N236" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B236, $C$2:$C$778, C236, $D$2:$D$778, D236, $E$2:$E$778, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O236" s="10"/>
@@ -23949,7 +23953,7 @@
       </c>
       <c r="J237" s="40"/>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B237, $C$2:$C$778, C237, $D$2:$D$778, D237, $E$2:$E$778, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23983,7 +23987,7 @@
       </c>
       <c r="J238" s="40"/>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B238, $C$2:$C$778, C238, $D$2:$D$778, D238, $E$2:$E$778, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24017,7 +24021,7 @@
       </c>
       <c r="J239" s="40"/>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B239, $C$2:$C$778, C239, $D$2:$D$778, D239, $E$2:$E$778, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24051,7 +24055,7 @@
       </c>
       <c r="J240" s="40"/>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B240, $C$2:$C$778, C240, $D$2:$D$778, D240, $E$2:$E$778, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24097,7 +24101,7 @@
         <v>250</v>
       </c>
       <c r="N241" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B241, $C$2:$C$778, C241, $D$2:$D$778, D241, $E$2:$E$778, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O241" s="10"/>
@@ -24134,7 +24138,7 @@
         <v>118</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B242, $C$2:$C$778, C242, $D$2:$D$778, D242, $E$2:$E$778, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24168,7 +24172,7 @@
       </c>
       <c r="J243" s="40"/>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B243, $C$2:$C$778, C243, $D$2:$D$778, D243, $E$2:$E$778, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24202,7 +24206,7 @@
       </c>
       <c r="J244" s="40"/>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B244, $C$2:$C$778, C244, $D$2:$D$778, D244, $E$2:$E$778, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24238,7 +24242,7 @@
         <v>118</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B245, $C$2:$C$778, C245, $D$2:$D$778, D245, $E$2:$E$778, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="35"/>
@@ -24285,7 +24289,7 @@
         <v>300</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B246, $C$2:$C$778, C246, $D$2:$D$778, D246, $E$2:$E$778, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24319,7 +24323,7 @@
       </c>
       <c r="J247" s="40"/>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B247, $C$2:$C$778, C247, $D$2:$D$778, D247, $E$2:$E$778, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24353,7 +24357,7 @@
       </c>
       <c r="J248" s="40"/>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B248, $C$2:$C$778, C248, $D$2:$D$778, D248, $E$2:$E$778, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24389,7 +24393,7 @@
         <v>118</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B249, $C$2:$C$778, C249, $D$2:$D$778, D249, $E$2:$E$778, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O249" s="35"/>
@@ -24424,7 +24428,7 @@
       </c>
       <c r="J250" s="40"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B250, $C$2:$C$778, C250, $D$2:$D$778, D250, $E$2:$E$778, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24458,7 +24462,7 @@
       </c>
       <c r="J251" s="40"/>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B251, $C$2:$C$778, C251, $D$2:$D$778, D251, $E$2:$E$778, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24492,7 +24496,7 @@
       </c>
       <c r="J252" s="40"/>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B252, $C$2:$C$778, C252, $D$2:$D$778, D252, $E$2:$E$778, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24528,7 +24532,7 @@
         <v>117</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B253, $C$2:$C$778, C253, $D$2:$D$778, D253, $E$2:$E$778, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24564,7 +24568,7 @@
         <v>118</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B254, $C$2:$C$778, C254, $D$2:$D$778, D254, $E$2:$E$778, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24598,7 +24602,7 @@
       </c>
       <c r="J255" s="40"/>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B255, $C$2:$C$778, C255, $D$2:$D$778, D255, $E$2:$E$778, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24632,7 +24636,7 @@
       </c>
       <c r="J256" s="40"/>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B256, $C$2:$C$778, C256, $D$2:$D$778, D256, $E$2:$E$778, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24666,7 +24670,7 @@
       </c>
       <c r="J257" s="40"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B257, $C$2:$C$778, C257, $D$2:$D$778, D257, $E$2:$E$778, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O257" s="35"/>
@@ -24701,7 +24705,7 @@
       </c>
       <c r="J258" s="40"/>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B258, $C$2:$C$778, C258, $D$2:$D$778, D258, $E$2:$E$778, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N284" si="8">IF(COUNTIFS( $B$2:$B$778, B258, $C$2:$C$778, C258, $D$2:$D$778, D258, $E$2:$E$778, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -24735,7 +24739,7 @@
       </c>
       <c r="J259" s="40"/>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B259, $C$2:$C$778, C259, $D$2:$D$778, D259, $E$2:$E$778, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24772,7 +24776,7 @@
       <c r="L260" s="18"/>
       <c r="M260" s="18"/>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B260, $C$2:$C$778, C260, $D$2:$D$778, D260, $E$2:$E$778, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="10"/>
@@ -24809,7 +24813,7 @@
         <v>55</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B261, $C$2:$C$778, C261, $D$2:$D$778, D261, $E$2:$E$778, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24855,7 +24859,7 @@
         <v>250</v>
       </c>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B262, $C$2:$C$778, C262, $D$2:$D$778, D262, $E$2:$E$778, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24889,7 +24893,7 @@
       </c>
       <c r="J263" s="40"/>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B263, $C$2:$C$778, C263, $D$2:$D$778, D263, $E$2:$E$778, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24923,7 +24927,7 @@
       </c>
       <c r="J264" s="40"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B264, $C$2:$C$778, C264, $D$2:$D$778, D264, $E$2:$E$778, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24959,7 +24963,7 @@
         <v>118</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B265, $C$2:$C$778, C265, $D$2:$D$778, D265, $E$2:$E$778, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24995,7 +24999,7 @@
         <v>118</v>
       </c>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B266, $C$2:$C$778, C266, $D$2:$D$778, D266, $E$2:$E$778, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25031,7 +25035,7 @@
         <v>118</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B267, $C$2:$C$778, C267, $D$2:$D$778, D267, $E$2:$E$778, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25065,7 +25069,7 @@
       </c>
       <c r="J268" s="40"/>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B268, $C$2:$C$778, C268, $D$2:$D$778, D268, $E$2:$E$778, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25102,7 +25106,7 @@
       <c r="L269" s="18"/>
       <c r="M269" s="18"/>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B269, $C$2:$C$778, C269, $D$2:$D$778, D269, $E$2:$E$778, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O269" s="10"/>
@@ -25137,7 +25141,7 @@
       </c>
       <c r="J270" s="40"/>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B270, $C$2:$C$778, C270, $D$2:$D$778, D270, $E$2:$E$778, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25183,7 +25187,7 @@
         <v>250</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B271, $C$2:$C$778, C271, $D$2:$D$778, D271, $E$2:$E$778, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25217,7 +25221,7 @@
       </c>
       <c r="J272" s="40"/>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B272, $C$2:$C$778, C272, $D$2:$D$778, D272, $E$2:$E$778, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25251,7 +25255,7 @@
       </c>
       <c r="J273" s="40"/>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B273, $C$2:$C$778, C273, $D$2:$D$778, D273, $E$2:$E$778, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25285,7 +25289,7 @@
       </c>
       <c r="J274" s="40"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B274, $C$2:$C$778, C274, $D$2:$D$778, D274, $E$2:$E$778, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O274" s="35"/>
@@ -25320,7 +25324,7 @@
       </c>
       <c r="J275" s="40"/>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B275, $C$2:$C$778, C275, $D$2:$D$778, D275, $E$2:$E$778, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25344,7 +25348,7 @@
         <v>5</v>
       </c>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B276, $C$2:$C$778, C276, $D$2:$D$778, D276, $E$2:$E$778, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25379,7 +25383,7 @@
         <v>646</v>
       </c>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B277, $C$2:$C$778, C277, $D$2:$D$778, D277, $E$2:$E$778, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25410,11 +25414,11 @@
         <v>11660</v>
       </c>
       <c r="M278" s="18">
-        <f t="shared" ref="M278:M284" si="4">ABS((D278*E278)-L278)</f>
+        <f t="shared" ref="M278:M284" si="9">ABS((D278*E278)-L278)</f>
         <v>300</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B278, $C$2:$C$778, C278, $D$2:$D$778, D278, $E$2:$E$778, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25445,11 +25449,11 @@
         <v>16807</v>
       </c>
       <c r="M279" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>651</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B279, $C$2:$C$778, C279, $D$2:$D$778, D279, $E$2:$E$778, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25480,11 +25484,11 @@
         <v>3400</v>
       </c>
       <c r="M280" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>250</v>
       </c>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B280, $C$2:$C$778, C280, $D$2:$D$778, D280, $E$2:$E$778, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25515,11 +25519,11 @@
         <v>20070</v>
       </c>
       <c r="M281" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>810</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B281, $C$2:$C$778, C281, $D$2:$D$778, D281, $E$2:$E$778, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25550,11 +25554,11 @@
         <v>19690</v>
       </c>
       <c r="M282" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>550</v>
       </c>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B282, $C$2:$C$778, C282, $D$2:$D$778, D282, $E$2:$E$778, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25585,11 +25589,11 @@
         <v>4852</v>
       </c>
       <c r="M283" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B283, $C$2:$C$778, C283, $D$2:$D$778, D283, $E$2:$E$778, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25620,11 +25624,11 @@
         <v>15600</v>
       </c>
       <c r="M284" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>525</v>
       </c>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$778, B284, $C$2:$C$778, C284, $D$2:$D$778, D284, $E$2:$E$778, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>

--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_9sep26_Wed.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_9sep26_Wed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0640F3C-CB7C-41B2-9444-B350F8FB0E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FE69FF-5C1C-481A-B9C4-5DC6F008ED94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3033,7 +3033,7 @@
       <c r="O34" s="10"/>
       <c r="P34" s="10"/>
     </row>
-    <row r="35" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="6" t="s">
         <v>62</v>
       </c>
@@ -4538,7 +4538,7 @@
       <c r="O71"/>
       <c r="P71"/>
     </row>
-    <row r="72" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="6" t="s">
         <v>62</v>
       </c>
@@ -4664,7 +4664,7 @@
       <c r="O74"/>
       <c r="P74" s="34"/>
     </row>
-    <row r="75" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="6" t="s">
         <v>62</v>
       </c>
@@ -4989,7 +4989,7 @@
       <c r="O82"/>
       <c r="P82"/>
     </row>
-    <row r="83" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="6" t="s">
         <v>62</v>
       </c>
@@ -5145,7 +5145,7 @@
       <c r="O86"/>
       <c r="P86"/>
     </row>
-    <row r="87" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="6" t="s">
         <v>62</v>
       </c>
@@ -5223,7 +5223,7 @@
       <c r="O88"/>
       <c r="P88"/>
     </row>
-    <row r="89" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="6" t="s">
         <v>62</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>250</v>
       </c>
       <c r="E94" s="4">
-        <v>227.8</v>
+        <v>225.5</v>
       </c>
       <c r="F94" s="4">
         <v>2.4787439830000002</v>
@@ -5459,15 +5459,13 @@
       </c>
       <c r="M94" s="18">
         <f t="shared" ref="M94:M109" si="3">ABS((D94*E94)-L94)</f>
-        <v>1567.5</v>
+        <v>992.5</v>
       </c>
       <c r="N94" t="str">
         <f t="shared" ref="N94:N129" si="4">IF(COUNTIFS( $B$2:$B$777, B94, $C$2:$C$777, C94, $D$2:$D$777, D94, $E$2:$E$777, E94) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O94" s="46" t="s">
-        <v>258</v>
-      </c>
+      <c r="O94" s="71"/>
       <c r="P94"/>
     </row>
     <row r="95" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -7371,7 +7369,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="136" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -7415,6 +7413,9 @@
       <c r="N136" s="10" t="str">
         <f t="shared" si="6"/>
         <v>Unique</v>
+      </c>
+      <c r="O136" s="46" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="137" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8245,7 +8246,7 @@
       </c>
       <c r="P154" s="35"/>
     </row>
-    <row r="155" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="3">
         <v>46274.414907407408</v>
       </c>
@@ -8919,7 +8920,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="170" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="11">
         <v>46252.6875</v>
       </c>
@@ -10315,7 +10316,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="203" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="8" t="s">
         <v>62</v>
       </c>
@@ -10351,7 +10352,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="204" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="3">
         <v>46260.375</v>
       </c>
@@ -10397,7 +10398,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="205" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="3">
         <v>46269.643055555556</v>
       </c>
@@ -11026,7 +11027,7 @@
       </c>
       <c r="P219" s="35"/>
     </row>
-    <row r="220" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="3">
         <v>46259.375</v>
       </c>
@@ -11214,7 +11215,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="225" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="3">
         <v>46260.554861111108</v>
       </c>
@@ -13458,7 +13459,7 @@
   <autoFilter ref="A1:P283" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="NETWEBEQ"/>
+        <filter val="APOLLOTYREEQ"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_9sep26_Wed.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_9sep26_Wed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FE69FF-5C1C-481A-B9C4-5DC6F008ED94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1254C4BF-F4D0-4E78-B619-3227D2F113EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1640,7 +1640,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="2" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
@@ -1846,7 +1846,7 @@
       <c r="O6" s="25"/>
       <c r="P6" s="10"/>
     </row>
-    <row r="7" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>62</v>
       </c>
@@ -2275,7 +2275,7 @@
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
     </row>
-    <row r="17" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="6" t="s">
         <v>62</v>
       </c>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="O104" s="10"/>
     </row>
-    <row r="105" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3">
         <v>46266.375</v>
       </c>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="P105" s="10"/>
     </row>
-    <row r="106" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3">
         <v>46267.513888888891</v>
       </c>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P112" s="10"/>
     </row>
-    <row r="113" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -6519,7 +6519,7 @@
       <c r="O116" s="10"/>
       <c r="P116" s="10"/>
     </row>
-    <row r="117" spans="1:16" s="26" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:16" s="26" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3">
         <v>46265.390277777777</v>
       </c>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="P123" s="26"/>
     </row>
-    <row r="124" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:16" s="25" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="P128" s="35"/>
     </row>
-    <row r="129" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="3">
         <v>46262.463194444441</v>
       </c>
@@ -7369,7 +7369,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="136" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -7418,7 +7418,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="137" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3">
         <v>46262.375</v>
       </c>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O141" s="35"/>
     </row>
-    <row r="142" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -8387,7 +8387,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="158" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="11">
         <v>46252.6875</v>
       </c>
@@ -8920,7 +8920,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="170" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="11">
         <v>46252.6875</v>
       </c>
@@ -8956,7 +8956,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="171" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="11">
         <v>46252.6875</v>
       </c>
@@ -10316,7 +10316,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="203" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="8" t="s">
         <v>62</v>
       </c>
@@ -10352,7 +10352,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="204" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="3">
         <v>46260.375</v>
       </c>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="P219" s="35"/>
     </row>
-    <row r="220" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="3">
         <v>46259.375</v>
       </c>
@@ -13459,7 +13459,7 @@
   <autoFilter ref="A1:P283" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="APOLLOTYREEQ"/>
+        <filter val="GRSEEQ"/>
       </filters>
     </filterColumn>
   </autoFilter>
